--- a/Files/Controls.xlsx
+++ b/Files/Controls.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\NVDA\VismaAdministration\Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Otto\Dokument\src\VismaAdministration-NVDAAddOn\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C7CBC2-89B6-4BAE-B305-F7AE47CCEA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D8BE0A-98D9-459D-840A-099BEC45595A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="30915" windowHeight="16876" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2470" yWindow="2470" windowWidth="14400" windowHeight="7290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1907" uniqueCount="538">
   <si>
     <t>WindowClassName</t>
   </si>
@@ -1367,9 +1367,6 @@
     <t>Anteckning, rad 3</t>
   </si>
   <si>
-    <t>Grid</t>
-  </si>
-  <si>
     <t>Beställningsrader</t>
   </si>
   <si>
@@ -1491,6 +1488,165 @@
   </si>
   <si>
     <t>Spårningsval</t>
+  </si>
+  <si>
+    <t>Skapa nytt</t>
+  </si>
+  <si>
+    <t>Skapa nytt år</t>
+  </si>
+  <si>
+    <t>Företagstyp</t>
+  </si>
+  <si>
+    <t>Enskild firma BAS 2025</t>
+  </si>
+  <si>
+    <t>Swish</t>
+  </si>
+  <si>
+    <t>IBAN/bankkontonummer</t>
+  </si>
+  <si>
+    <t>Adress 2</t>
+  </si>
+  <si>
+    <t>Leveransnamn</t>
+  </si>
+  <si>
+    <t>Leveransadress</t>
+  </si>
+  <si>
+    <t>Leveransadress 2</t>
+  </si>
+  <si>
+    <t>Utskriftsval</t>
+  </si>
+  <si>
+    <t>Avvik. Land</t>
+  </si>
+  <si>
+    <t>Bilaga</t>
+  </si>
+  <si>
+    <t>Momskod frakt</t>
+  </si>
+  <si>
+    <t>Momskod expeditionsavgift</t>
+  </si>
+  <si>
+    <t>Ordernummer/datum</t>
+  </si>
+  <si>
+    <t>Ursprungsorder</t>
+  </si>
+  <si>
+    <t>Betalningar</t>
+  </si>
+  <si>
+    <t>Nästa period, start</t>
+  </si>
+  <si>
+    <t>Avtalens startdatum, månad</t>
+  </si>
+  <si>
+    <t>Avtalens startdatum, dag</t>
+  </si>
+  <si>
+    <t>Avvikande leveransadress, VAT-nummer</t>
+  </si>
+  <si>
+    <t>Avtalstid, månader</t>
+  </si>
+  <si>
+    <t>Första fakturan kan skapas, månad</t>
+  </si>
+  <si>
+    <t>Första fakturan kan skapas, dag</t>
+  </si>
+  <si>
+    <t>Mallnummer</t>
+  </si>
+  <si>
+    <t>Skapade avtal</t>
+  </si>
+  <si>
+    <t>Kopia till kund</t>
+  </si>
+  <si>
+    <t>Extra orderdokument</t>
+  </si>
+  <si>
+    <t>Faktura</t>
+  </si>
+  <si>
+    <t>Kreditfaktura</t>
+  </si>
+  <si>
+    <t>Räntefaktura</t>
+  </si>
+  <si>
+    <t>Kontantnota</t>
+  </si>
+  <si>
+    <t>Extra fakturadokument</t>
+  </si>
+  <si>
+    <t>Kod</t>
+  </si>
+  <si>
+    <t>Anteckning</t>
+  </si>
+  <si>
+    <t>Från, rad 1</t>
+  </si>
+  <si>
+    <t>Avrundning, rad 1</t>
+  </si>
+  <si>
+    <t>Från, rad 2</t>
+  </si>
+  <si>
+    <t>Avrundning, rad 2</t>
+  </si>
+  <si>
+    <t>Från, rad 3</t>
+  </si>
+  <si>
+    <t>Avrundning, rad 3</t>
+  </si>
+  <si>
+    <t>Från, rad 4</t>
+  </si>
+  <si>
+    <t>Avrundning, rad 4</t>
+  </si>
+  <si>
+    <t>Procent</t>
+  </si>
+  <si>
+    <t>Belopp</t>
+  </si>
+  <si>
+    <t>Leverantörsprislista</t>
+  </si>
+  <si>
+    <t>Radrabatt</t>
+  </si>
+  <si>
+    <t>Fakturarabatt</t>
+  </si>
+  <si>
+    <t>Artikelgrupper</t>
+  </si>
+  <si>
+    <t>Lista</t>
+  </si>
+  <si>
+    <t>Plusgiro</t>
+  </si>
+  <si>
+    <t>Skuldkonto</t>
   </si>
 </sst>
 </file>
@@ -1526,14 +1682,83 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1550,10 +1775,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr val="windowText" lastClr="3D3D3D"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFAEF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -1808,14 +2033,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E585"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:E706"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="3" max="3" width="26.06640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.04296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="44.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1832,7 +2057,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -1846,7 +2071,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -1860,7 +2085,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -1874,7 +2099,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -1888,7 +2113,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -1902,7 +2127,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -1916,7 +2141,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -1930,7 +2155,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -1944,7 +2169,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -1958,7 +2183,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -1972,7 +2197,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1986,7 +2211,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -2000,7 +2225,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -2014,7 +2239,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -2028,7 +2253,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -2042,7 +2267,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -2056,7 +2281,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -2070,7 +2295,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -2084,7 +2309,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -2098,7 +2323,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -2112,7 +2337,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -2126,7 +2351,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -2140,9 +2365,9 @@
         <v>272</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A24" t="e">
-        <v>#NAME?</v>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A24" t="s">
+        <v>28</v>
       </c>
       <c r="B24">
         <v>21679</v>
@@ -2150,11 +2375,14 @@
       <c r="C24" t="s">
         <v>250</v>
       </c>
+      <c r="D24" t="s">
+        <v>535</v>
+      </c>
       <c r="E24" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -2168,7 +2396,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -2182,7 +2410,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -2193,7 +2421,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -2204,7 +2432,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -2215,7 +2443,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -2226,7 +2454,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A31" t="s">
         <v>28</v>
       </c>
@@ -2240,7 +2468,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A32" t="s">
         <v>3</v>
       </c>
@@ -2251,7 +2479,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -2265,7 +2493,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -2276,7 +2504,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -2287,7 +2515,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -2298,7 +2526,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -2309,7 +2537,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -2320,7 +2548,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -2331,7 +2559,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -2342,7 +2570,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A41" t="s">
         <v>15</v>
       </c>
@@ -2353,7 +2581,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -2364,7 +2592,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -2375,7 +2603,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A44" t="s">
         <v>19</v>
       </c>
@@ -2386,7 +2614,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A45" t="s">
         <v>19</v>
       </c>
@@ -2397,7 +2625,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -2408,7 +2636,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A47" t="s">
         <v>19</v>
       </c>
@@ -2419,7 +2647,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A48" t="s">
         <v>19</v>
       </c>
@@ -2430,7 +2658,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -2441,7 +2669,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -2452,7 +2680,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -2463,7 +2691,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A52" t="s">
         <v>6</v>
       </c>
@@ -2474,7 +2702,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A53" t="s">
         <v>6</v>
       </c>
@@ -2488,7 +2716,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A54" t="s">
         <v>6</v>
       </c>
@@ -2499,7 +2727,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -2510,7 +2738,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A56" t="s">
         <v>6</v>
       </c>
@@ -2521,7 +2749,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A57" t="s">
         <v>6</v>
       </c>
@@ -2532,7 +2760,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A58" t="s">
         <v>19</v>
       </c>
@@ -2543,7 +2771,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -2557,7 +2785,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A60" t="s">
         <v>6</v>
       </c>
@@ -2568,7 +2796,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A61" t="s">
         <v>6</v>
       </c>
@@ -2579,7 +2807,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A62" t="s">
         <v>6</v>
       </c>
@@ -2590,7 +2818,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A63" t="s">
         <v>6</v>
       </c>
@@ -2601,7 +2829,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A64" t="s">
         <v>6</v>
       </c>
@@ -2612,7 +2840,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A65" t="s">
         <v>6</v>
       </c>
@@ -2623,7 +2851,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A66" t="s">
         <v>6</v>
       </c>
@@ -2634,7 +2862,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A67" t="s">
         <v>15</v>
       </c>
@@ -2648,7 +2876,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A68" t="s">
         <v>6</v>
       </c>
@@ -2665,7 +2893,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -2679,7 +2907,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A70" t="s">
         <v>6</v>
       </c>
@@ -2690,7 +2918,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A71" t="s">
         <v>6</v>
       </c>
@@ -2701,7 +2929,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A72" t="s">
         <v>6</v>
       </c>
@@ -2712,7 +2940,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A73" t="s">
         <v>6</v>
       </c>
@@ -2723,7 +2951,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A74" t="s">
         <v>6</v>
       </c>
@@ -2734,7 +2962,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A75" t="s">
         <v>6</v>
       </c>
@@ -2745,7 +2973,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A76" t="s">
         <v>6</v>
       </c>
@@ -2756,7 +2984,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A77" t="s">
         <v>6</v>
       </c>
@@ -2767,7 +2995,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A78" t="s">
         <v>6</v>
       </c>
@@ -2778,7 +3006,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A79" t="s">
         <v>6</v>
       </c>
@@ -2789,7 +3017,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A80" t="s">
         <v>6</v>
       </c>
@@ -2800,7 +3028,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A81" t="s">
         <v>6</v>
       </c>
@@ -2811,7 +3039,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A82" t="s">
         <v>6</v>
       </c>
@@ -2825,7 +3053,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A83" t="s">
         <v>6</v>
       </c>
@@ -2839,7 +3067,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A84" t="s">
         <v>6</v>
       </c>
@@ -2853,7 +3081,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A85" t="s">
         <v>6</v>
       </c>
@@ -2867,7 +3095,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A86" t="s">
         <v>6</v>
       </c>
@@ -2881,7 +3109,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A87" t="s">
         <v>6</v>
       </c>
@@ -2895,7 +3123,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A88" t="s">
         <v>6</v>
       </c>
@@ -2906,7 +3134,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A89" t="s">
         <v>6</v>
       </c>
@@ -2917,7 +3145,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A90" t="s">
         <v>6</v>
       </c>
@@ -2928,7 +3156,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A91" t="s">
         <v>6</v>
       </c>
@@ -2939,7 +3167,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A92" t="s">
         <v>6</v>
       </c>
@@ -2950,7 +3178,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A93" t="s">
         <v>6</v>
       </c>
@@ -2961,7 +3189,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A94" t="s">
         <v>19</v>
       </c>
@@ -2972,7 +3200,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A95" t="s">
         <v>6</v>
       </c>
@@ -2983,7 +3211,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A96" t="s">
         <v>19</v>
       </c>
@@ -2994,7 +3222,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A97" t="s">
         <v>19</v>
       </c>
@@ -3005,7 +3233,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A98" t="s">
         <v>19</v>
       </c>
@@ -3016,7 +3244,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A99" t="s">
         <v>19</v>
       </c>
@@ -3027,7 +3255,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A100" t="s">
         <v>19</v>
       </c>
@@ -3041,7 +3269,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A101" t="s">
         <v>19</v>
       </c>
@@ -3055,7 +3283,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A102" t="s">
         <v>19</v>
       </c>
@@ -3066,7 +3294,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A103" t="s">
         <v>19</v>
       </c>
@@ -3077,7 +3305,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A104" t="s">
         <v>19</v>
       </c>
@@ -3088,7 +3316,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A105" t="s">
         <v>19</v>
       </c>
@@ -3099,7 +3327,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A106" t="s">
         <v>15</v>
       </c>
@@ -3113,7 +3341,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A107" t="s">
         <v>15</v>
       </c>
@@ -3127,7 +3355,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A108" t="s">
         <v>15</v>
       </c>
@@ -3138,7 +3366,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A109" t="s">
         <v>6</v>
       </c>
@@ -3152,7 +3380,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A110" t="s">
         <v>6</v>
       </c>
@@ -3163,7 +3391,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A111" t="s">
         <v>6</v>
       </c>
@@ -3174,7 +3402,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A112" t="s">
         <v>6</v>
       </c>
@@ -3185,7 +3413,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A113" t="s">
         <v>6</v>
       </c>
@@ -3196,7 +3424,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A114" t="s">
         <v>6</v>
       </c>
@@ -3207,7 +3435,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A115" t="s">
         <v>6</v>
       </c>
@@ -3218,7 +3446,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A116" t="s">
         <v>6</v>
       </c>
@@ -3229,7 +3457,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A117" t="s">
         <v>6</v>
       </c>
@@ -3240,7 +3468,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A118" t="s">
         <v>6</v>
       </c>
@@ -3251,7 +3479,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A119" t="s">
         <v>6</v>
       </c>
@@ -3262,7 +3490,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A120" t="s">
         <v>6</v>
       </c>
@@ -3273,7 +3501,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A121" t="s">
         <v>6</v>
       </c>
@@ -3284,7 +3512,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A122" t="s">
         <v>6</v>
       </c>
@@ -3295,7 +3523,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A123" t="s">
         <v>6</v>
       </c>
@@ -3306,7 +3534,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A124" t="s">
         <v>6</v>
       </c>
@@ -3317,7 +3545,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A125" t="s">
         <v>6</v>
       </c>
@@ -3328,7 +3556,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A126" t="s">
         <v>6</v>
       </c>
@@ -3339,7 +3567,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A127" t="s">
         <v>6</v>
       </c>
@@ -3350,7 +3578,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A128" t="s">
         <v>6</v>
       </c>
@@ -3361,7 +3589,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A129" t="s">
         <v>6</v>
       </c>
@@ -3372,7 +3600,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A130" t="s">
         <v>6</v>
       </c>
@@ -3383,7 +3611,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A131" t="s">
         <v>6</v>
       </c>
@@ -3394,7 +3622,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A132" t="s">
         <v>19</v>
       </c>
@@ -3405,7 +3633,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A133" t="s">
         <v>19</v>
       </c>
@@ -3416,7 +3644,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A134" t="s">
         <v>19</v>
       </c>
@@ -3427,7 +3655,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A135" t="s">
         <v>19</v>
       </c>
@@ -3438,7 +3666,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A136" t="s">
         <v>19</v>
       </c>
@@ -3449,7 +3677,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A137" t="s">
         <v>19</v>
       </c>
@@ -3460,7 +3688,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A138" t="s">
         <v>19</v>
       </c>
@@ -3471,7 +3699,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A139" t="s">
         <v>19</v>
       </c>
@@ -3482,7 +3710,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A140" t="s">
         <v>6</v>
       </c>
@@ -3493,7 +3721,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A141" t="s">
         <v>6</v>
       </c>
@@ -3504,7 +3732,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A142" t="s">
         <v>6</v>
       </c>
@@ -3515,7 +3743,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A143" t="s">
         <v>6</v>
       </c>
@@ -3526,7 +3754,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A144" t="s">
         <v>19</v>
       </c>
@@ -3537,7 +3765,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A145" t="s">
         <v>19</v>
       </c>
@@ -3548,7 +3776,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A146" t="s">
         <v>6</v>
       </c>
@@ -3565,7 +3793,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A147" t="s">
         <v>6</v>
       </c>
@@ -3579,7 +3807,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A148" t="s">
         <v>6</v>
       </c>
@@ -3590,7 +3818,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A149" t="s">
         <v>6</v>
       </c>
@@ -3601,7 +3829,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A150" t="s">
         <v>6</v>
       </c>
@@ -3612,7 +3840,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A151" t="s">
         <v>6</v>
       </c>
@@ -3623,7 +3851,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A152" t="s">
         <v>6</v>
       </c>
@@ -3634,7 +3862,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A153" t="s">
         <v>19</v>
       </c>
@@ -3645,7 +3873,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A154" t="s">
         <v>6</v>
       </c>
@@ -3656,7 +3884,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A155" t="s">
         <v>6</v>
       </c>
@@ -3667,7 +3895,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A156" t="s">
         <v>6</v>
       </c>
@@ -3678,7 +3906,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A157" t="s">
         <v>6</v>
       </c>
@@ -3689,7 +3917,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A158" t="s">
         <v>6</v>
       </c>
@@ -3700,7 +3928,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A159" t="s">
         <v>6</v>
       </c>
@@ -3711,7 +3939,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A160" t="s">
         <v>6</v>
       </c>
@@ -3722,7 +3950,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A161" t="s">
         <v>6</v>
       </c>
@@ -3733,7 +3961,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A162" t="s">
         <v>6</v>
       </c>
@@ -3744,7 +3972,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A163" t="s">
         <v>6</v>
       </c>
@@ -3755,7 +3983,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A164" t="s">
         <v>6</v>
       </c>
@@ -3772,7 +4000,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A165" t="s">
         <v>6</v>
       </c>
@@ -3786,7 +4014,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A166" t="s">
         <v>6</v>
       </c>
@@ -3800,7 +4028,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A167" t="s">
         <v>6</v>
       </c>
@@ -3814,7 +4042,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A168" t="s">
         <v>6</v>
       </c>
@@ -3828,7 +4056,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A169" t="s">
         <v>6</v>
       </c>
@@ -3842,7 +4070,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A170" t="s">
         <v>6</v>
       </c>
@@ -3853,7 +4081,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A171" t="s">
         <v>6</v>
       </c>
@@ -3864,7 +4092,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A172" t="s">
         <v>6</v>
       </c>
@@ -3875,7 +4103,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A173" t="s">
         <v>6</v>
       </c>
@@ -3886,7 +4114,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A174" t="s">
         <v>6</v>
       </c>
@@ -3900,13 +4128,16 @@
         <v>156</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A175" t="s">
         <v>6</v>
       </c>
       <c r="B175">
         <v>23179</v>
       </c>
+      <c r="C175" t="s">
+        <v>252</v>
+      </c>
       <c r="D175" t="s">
         <v>158</v>
       </c>
@@ -3914,403 +4145,511 @@
         <v>157</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A176" t="s">
         <v>6</v>
       </c>
       <c r="B176">
         <v>23180</v>
       </c>
+      <c r="C176" t="s">
+        <v>252</v>
+      </c>
       <c r="D176" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A177" t="s">
         <v>6</v>
       </c>
       <c r="B177">
         <v>23191</v>
       </c>
+      <c r="C177" t="s">
+        <v>252</v>
+      </c>
       <c r="D177" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A178" t="s">
         <v>19</v>
       </c>
       <c r="B178">
         <v>15162</v>
       </c>
+      <c r="C178" t="s">
+        <v>252</v>
+      </c>
       <c r="D178" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A179" t="s">
         <v>6</v>
       </c>
       <c r="B179">
         <v>23181</v>
       </c>
+      <c r="C179" t="s">
+        <v>252</v>
+      </c>
       <c r="D179" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A180" t="s">
         <v>6</v>
       </c>
       <c r="B180">
         <v>23182</v>
       </c>
+      <c r="C180" t="s">
+        <v>252</v>
+      </c>
       <c r="D180" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A181" t="s">
         <v>6</v>
       </c>
       <c r="B181">
         <v>23221</v>
       </c>
+      <c r="C181" t="s">
+        <v>252</v>
+      </c>
       <c r="D181" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A182" t="s">
         <v>6</v>
       </c>
       <c r="B182">
         <v>23734</v>
       </c>
+      <c r="C182" t="s">
+        <v>252</v>
+      </c>
       <c r="D182" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A183" t="s">
         <v>6</v>
       </c>
       <c r="B183">
         <v>23183</v>
       </c>
+      <c r="C183" t="s">
+        <v>252</v>
+      </c>
       <c r="D183" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A184" t="s">
         <v>6</v>
       </c>
       <c r="B184">
         <v>23184</v>
       </c>
+      <c r="C184" t="s">
+        <v>252</v>
+      </c>
       <c r="D184" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A185" t="s">
         <v>6</v>
       </c>
       <c r="B185">
         <v>23185</v>
       </c>
+      <c r="C185" t="s">
+        <v>252</v>
+      </c>
       <c r="D185" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A186" t="s">
         <v>6</v>
       </c>
       <c r="B186">
         <v>23210</v>
       </c>
+      <c r="C186" t="s">
+        <v>252</v>
+      </c>
       <c r="D186" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A187" t="s">
         <v>6</v>
       </c>
       <c r="B187">
         <v>23186</v>
       </c>
+      <c r="C187" t="s">
+        <v>252</v>
+      </c>
       <c r="D187" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A188" t="s">
         <v>6</v>
       </c>
       <c r="B188">
         <v>23187</v>
       </c>
+      <c r="C188" t="s">
+        <v>252</v>
+      </c>
       <c r="D188" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A189" t="s">
         <v>6</v>
       </c>
       <c r="B189">
         <v>23188</v>
       </c>
+      <c r="C189" t="s">
+        <v>252</v>
+      </c>
       <c r="D189" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A190" t="s">
         <v>6</v>
       </c>
       <c r="B190">
         <v>23189</v>
       </c>
+      <c r="C190" t="s">
+        <v>252</v>
+      </c>
       <c r="D190" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A191" t="s">
         <v>6</v>
       </c>
       <c r="B191">
         <v>23787</v>
       </c>
+      <c r="C191" t="s">
+        <v>252</v>
+      </c>
       <c r="D191" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A192" t="s">
         <v>6</v>
       </c>
       <c r="B192">
         <v>23190</v>
       </c>
+      <c r="C192" t="s">
+        <v>252</v>
+      </c>
       <c r="D192" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A193" t="s">
         <v>6</v>
       </c>
       <c r="B193">
         <v>20748</v>
       </c>
+      <c r="C193" t="s">
+        <v>252</v>
+      </c>
       <c r="D193" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A194" t="s">
         <v>19</v>
       </c>
       <c r="B194">
         <v>24921</v>
       </c>
+      <c r="C194" t="s">
+        <v>252</v>
+      </c>
       <c r="D194" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A195" t="s">
         <v>6</v>
       </c>
       <c r="B195">
         <v>23228</v>
       </c>
+      <c r="C195" t="s">
+        <v>252</v>
+      </c>
       <c r="D195" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A196" t="s">
         <v>6</v>
       </c>
       <c r="B196">
         <v>23229</v>
       </c>
+      <c r="C196" t="s">
+        <v>252</v>
+      </c>
       <c r="D196" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A197" t="s">
         <v>6</v>
       </c>
       <c r="B197">
         <v>23209</v>
       </c>
+      <c r="C197" t="s">
+        <v>252</v>
+      </c>
       <c r="D197" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A198" t="s">
         <v>6</v>
       </c>
       <c r="B198">
         <v>23206</v>
       </c>
+      <c r="C198" t="s">
+        <v>252</v>
+      </c>
       <c r="D198" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A199" t="s">
         <v>19</v>
       </c>
       <c r="B199">
         <v>25049</v>
       </c>
+      <c r="C199" t="s">
+        <v>252</v>
+      </c>
       <c r="D199" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A200" t="s">
         <v>19</v>
       </c>
       <c r="B200">
         <v>26256</v>
       </c>
+      <c r="C200" t="s">
+        <v>252</v>
+      </c>
       <c r="D200" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A201" t="s">
         <v>19</v>
       </c>
       <c r="B201">
         <v>23230</v>
       </c>
+      <c r="C201" t="s">
+        <v>252</v>
+      </c>
       <c r="D201" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A202" t="s">
         <v>19</v>
       </c>
       <c r="B202">
         <v>23220</v>
       </c>
+      <c r="C202" t="s">
+        <v>252</v>
+      </c>
       <c r="D202" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A203" t="s">
         <v>6</v>
       </c>
       <c r="B203">
         <v>23196</v>
       </c>
+      <c r="C203" t="s">
+        <v>252</v>
+      </c>
       <c r="D203" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A204" t="s">
         <v>6</v>
       </c>
       <c r="B204">
         <v>23194</v>
       </c>
+      <c r="C204" t="s">
+        <v>252</v>
+      </c>
       <c r="D204" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A205" t="s">
         <v>6</v>
       </c>
       <c r="B205">
         <v>23195</v>
       </c>
+      <c r="C205" t="s">
+        <v>252</v>
+      </c>
       <c r="D205" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A206" t="s">
         <v>6</v>
       </c>
       <c r="B206">
         <v>21770</v>
       </c>
+      <c r="C206" t="s">
+        <v>252</v>
+      </c>
       <c r="D206" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A207" t="s">
         <v>6</v>
       </c>
       <c r="B207">
         <v>24824</v>
       </c>
+      <c r="C207" t="s">
+        <v>252</v>
+      </c>
       <c r="D207" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A208" t="s">
         <v>6</v>
       </c>
       <c r="B208">
         <v>24825</v>
       </c>
+      <c r="C208" t="s">
+        <v>252</v>
+      </c>
       <c r="D208" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A209" t="s">
         <v>6</v>
       </c>
       <c r="B209">
         <v>23197</v>
       </c>
+      <c r="C209" t="s">
+        <v>252</v>
+      </c>
       <c r="D209" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A210" t="s">
         <v>6</v>
       </c>
       <c r="B210">
         <v>23193</v>
       </c>
+      <c r="C210" t="s">
+        <v>252</v>
+      </c>
       <c r="D210" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A211" t="s">
         <v>6</v>
       </c>
       <c r="B211">
         <v>23192</v>
       </c>
+      <c r="C211" t="s">
+        <v>252</v>
+      </c>
       <c r="D211" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A212" t="s">
         <v>6</v>
       </c>
@@ -4321,7 +4660,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A213" t="s">
         <v>6</v>
       </c>
@@ -4332,7 +4671,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A214" t="s">
         <v>6</v>
       </c>
@@ -4343,7 +4682,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A215" t="s">
         <v>6</v>
       </c>
@@ -4354,7 +4693,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A216" t="s">
         <v>6</v>
       </c>
@@ -4365,7 +4704,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A217" t="s">
         <v>6</v>
       </c>
@@ -4376,7 +4715,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A218" t="s">
         <v>6</v>
       </c>
@@ -4387,7 +4726,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A219" t="s">
         <v>19</v>
       </c>
@@ -4398,7 +4737,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A220" t="s">
         <v>6</v>
       </c>
@@ -4412,7 +4751,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A221" t="s">
         <v>6</v>
       </c>
@@ -4423,7 +4762,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A222" t="s">
         <v>6</v>
       </c>
@@ -4434,7 +4773,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A223" t="s">
         <v>6</v>
       </c>
@@ -4445,7 +4784,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A224" t="s">
         <v>6</v>
       </c>
@@ -4456,7 +4795,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A225" t="s">
         <v>6</v>
       </c>
@@ -4467,7 +4806,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A226" t="s">
         <v>6</v>
       </c>
@@ -4478,7 +4817,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A227" t="s">
         <v>6</v>
       </c>
@@ -4489,7 +4828,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A228" t="s">
         <v>6</v>
       </c>
@@ -4500,7 +4839,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A229" t="s">
         <v>15</v>
       </c>
@@ -4511,7 +4850,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A230" t="s">
         <v>19</v>
       </c>
@@ -4522,7 +4861,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A231" t="s">
         <v>19</v>
       </c>
@@ -4536,7 +4875,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A232" t="s">
         <v>19</v>
       </c>
@@ -4547,7 +4886,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A233" t="s">
         <v>6</v>
       </c>
@@ -4564,7 +4903,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A234" t="s">
         <v>6</v>
       </c>
@@ -4581,7 +4920,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A235" t="s">
         <v>6</v>
       </c>
@@ -4595,7 +4934,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A236" t="s">
         <v>6</v>
       </c>
@@ -4609,18 +4948,21 @@
         <v>278</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A237" t="s">
         <v>6</v>
       </c>
       <c r="B237">
         <v>22424</v>
       </c>
+      <c r="C237" t="s">
+        <v>237</v>
+      </c>
       <c r="D237" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A238" t="s">
         <v>6</v>
       </c>
@@ -4634,7 +4976,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A239" t="s">
         <v>6</v>
       </c>
@@ -4648,7 +4990,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A240" t="s">
         <v>6</v>
       </c>
@@ -4659,7 +5001,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A241" t="s">
         <v>6</v>
       </c>
@@ -4670,7 +5012,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A242" t="s">
         <v>6</v>
       </c>
@@ -4681,7 +5023,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A243" t="s">
         <v>6</v>
       </c>
@@ -4692,7 +5034,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A244" t="s">
         <v>6</v>
       </c>
@@ -4703,7 +5045,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A245" t="s">
         <v>6</v>
       </c>
@@ -4714,7 +5056,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A246" t="s">
         <v>6</v>
       </c>
@@ -4725,7 +5067,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A247" t="s">
         <v>6</v>
       </c>
@@ -4736,7 +5078,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A248" t="s">
         <v>6</v>
       </c>
@@ -4747,7 +5089,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A249" t="s">
         <v>6</v>
       </c>
@@ -4758,7 +5100,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A250" t="s">
         <v>6</v>
       </c>
@@ -4769,7 +5111,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A251" t="s">
         <v>6</v>
       </c>
@@ -4780,7 +5122,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A252" t="s">
         <v>6</v>
       </c>
@@ -4788,10 +5130,10 @@
         <v>22433</v>
       </c>
       <c r="D252" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.45">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A253" t="s">
         <v>6</v>
       </c>
@@ -4802,7 +5144,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A254" t="s">
         <v>6</v>
       </c>
@@ -4813,7 +5155,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A255" t="s">
         <v>6</v>
       </c>
@@ -4824,7 +5166,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A256" t="s">
         <v>6</v>
       </c>
@@ -4835,7 +5177,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A257" t="s">
         <v>6</v>
       </c>
@@ -4846,7 +5188,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A258" t="s">
         <v>6</v>
       </c>
@@ -4857,7 +5199,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A259" t="s">
         <v>6</v>
       </c>
@@ -4868,7 +5210,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A260" t="s">
         <v>6</v>
       </c>
@@ -4879,7 +5221,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A261" t="s">
         <v>6</v>
       </c>
@@ -4890,7 +5232,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A262" t="s">
         <v>6</v>
       </c>
@@ -4901,7 +5243,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A263" t="s">
         <v>6</v>
       </c>
@@ -4912,7 +5254,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A264" t="s">
         <v>6</v>
       </c>
@@ -4923,7 +5265,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A265" t="s">
         <v>6</v>
       </c>
@@ -4934,7 +5276,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A266" t="s">
         <v>6</v>
       </c>
@@ -4945,7 +5287,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A267" t="s">
         <v>6</v>
       </c>
@@ -4956,7 +5298,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A268" t="s">
         <v>6</v>
       </c>
@@ -4967,7 +5309,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A269" t="s">
         <v>6</v>
       </c>
@@ -4978,7 +5320,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A270" t="s">
         <v>6</v>
       </c>
@@ -4986,10 +5328,10 @@
         <v>22442</v>
       </c>
       <c r="D270" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.45">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A271" t="s">
         <v>6</v>
       </c>
@@ -5003,7 +5345,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A272" t="s">
         <v>6</v>
       </c>
@@ -5017,7 +5359,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A273" t="s">
         <v>6</v>
       </c>
@@ -5031,7 +5373,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A274" t="s">
         <v>6</v>
       </c>
@@ -5045,7 +5387,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A275" t="s">
         <v>6</v>
       </c>
@@ -5059,7 +5401,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A276" t="s">
         <v>6</v>
       </c>
@@ -5073,7 +5415,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A277" t="s">
         <v>6</v>
       </c>
@@ -5087,7 +5429,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A278" t="s">
         <v>6</v>
       </c>
@@ -5101,7 +5443,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A279" t="s">
         <v>6</v>
       </c>
@@ -5115,7 +5457,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A280" t="s">
         <v>6</v>
       </c>
@@ -5129,7 +5471,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A281" t="s">
         <v>6</v>
       </c>
@@ -5143,7 +5485,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A282" t="s">
         <v>6</v>
       </c>
@@ -5157,7 +5499,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A283" t="s">
         <v>15</v>
       </c>
@@ -5171,7 +5513,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A284" t="s">
         <v>6</v>
       </c>
@@ -5182,7 +5524,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A285" t="s">
         <v>6</v>
       </c>
@@ -5193,7 +5535,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A286" t="s">
         <v>6</v>
       </c>
@@ -5207,7 +5549,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A287" t="s">
         <v>6</v>
       </c>
@@ -5218,7 +5560,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A288" t="s">
         <v>6</v>
       </c>
@@ -5229,7 +5571,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A289" t="s">
         <v>6</v>
       </c>
@@ -5240,7 +5582,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A290" t="s">
         <v>6</v>
       </c>
@@ -5251,7 +5593,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A291" t="s">
         <v>6</v>
       </c>
@@ -5262,7 +5604,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A292" t="s">
         <v>6</v>
       </c>
@@ -5273,7 +5615,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A293" t="s">
         <v>6</v>
       </c>
@@ -5284,7 +5626,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A294" t="s">
         <v>6</v>
       </c>
@@ -5295,7 +5637,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A295" t="s">
         <v>6</v>
       </c>
@@ -5306,7 +5648,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A296" t="s">
         <v>6</v>
       </c>
@@ -5317,7 +5659,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A297" t="s">
         <v>6</v>
       </c>
@@ -5328,7 +5670,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A298" t="s">
         <v>6</v>
       </c>
@@ -5339,7 +5681,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A299" t="s">
         <v>6</v>
       </c>
@@ -5350,7 +5692,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A300" t="s">
         <v>6</v>
       </c>
@@ -5361,7 +5703,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A301" t="s">
         <v>6</v>
       </c>
@@ -5372,7 +5714,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A302" t="s">
         <v>6</v>
       </c>
@@ -5383,7 +5725,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A303" t="s">
         <v>6</v>
       </c>
@@ -5394,7 +5736,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A304" t="s">
         <v>6</v>
       </c>
@@ -5405,7 +5747,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A305" t="s">
         <v>6</v>
       </c>
@@ -5416,7 +5758,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A306" t="s">
         <v>6</v>
       </c>
@@ -5427,7 +5769,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A307" t="s">
         <v>15</v>
       </c>
@@ -5441,7 +5783,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A308" t="s">
         <v>15</v>
       </c>
@@ -5452,7 +5794,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A309" t="s">
         <v>15</v>
       </c>
@@ -5463,7 +5805,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A310" t="s">
         <v>15</v>
       </c>
@@ -5474,7 +5816,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A311" t="s">
         <v>15</v>
       </c>
@@ -5485,7 +5827,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A312" t="s">
         <v>15</v>
       </c>
@@ -5496,7 +5838,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A313" t="s">
         <v>15</v>
       </c>
@@ -5507,7 +5849,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A314" t="s">
         <v>19</v>
       </c>
@@ -5521,7 +5863,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A315" t="s">
         <v>19</v>
       </c>
@@ -5532,7 +5874,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A316" t="s">
         <v>6</v>
       </c>
@@ -5543,7 +5885,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A317" t="s">
         <v>6</v>
       </c>
@@ -5557,7 +5899,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A318" t="s">
         <v>6</v>
       </c>
@@ -5568,7 +5910,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A319" t="s">
         <v>6</v>
       </c>
@@ -5579,7 +5921,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A320" t="s">
         <v>6</v>
       </c>
@@ -5593,7 +5935,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A321" t="s">
         <v>6</v>
       </c>
@@ -5604,7 +5946,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A322" t="s">
         <v>6</v>
       </c>
@@ -5615,7 +5957,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A323" t="s">
         <v>6</v>
       </c>
@@ -5626,7 +5968,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A324" t="s">
         <v>6</v>
       </c>
@@ -5637,7 +5979,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A325" t="s">
         <v>6</v>
       </c>
@@ -5648,7 +5990,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A326" t="s">
         <v>6</v>
       </c>
@@ -5659,7 +6001,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A327" t="s">
         <v>6</v>
       </c>
@@ -5670,7 +6012,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A328" t="s">
         <v>6</v>
       </c>
@@ -5681,7 +6023,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A329" t="s">
         <v>6</v>
       </c>
@@ -5692,7 +6034,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A330" t="s">
         <v>6</v>
       </c>
@@ -5703,7 +6045,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A331" t="s">
         <v>6</v>
       </c>
@@ -5714,7 +6056,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A332" t="s">
         <v>6</v>
       </c>
@@ -5725,7 +6067,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A333" t="s">
         <v>6</v>
       </c>
@@ -5736,7 +6078,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A334" t="s">
         <v>15</v>
       </c>
@@ -5747,7 +6089,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A335" t="s">
         <v>6</v>
       </c>
@@ -5761,7 +6103,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A336" t="s">
         <v>6</v>
       </c>
@@ -5775,7 +6117,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A337" t="s">
         <v>6</v>
       </c>
@@ -5789,7 +6131,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A338" t="s">
         <v>6</v>
       </c>
@@ -5803,7 +6145,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A339" t="s">
         <v>6</v>
       </c>
@@ -5817,7 +6159,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A340" t="s">
         <v>6</v>
       </c>
@@ -5831,7 +6173,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A341" t="s">
         <v>6</v>
       </c>
@@ -5845,7 +6187,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A342" t="s">
         <v>6</v>
       </c>
@@ -5859,7 +6201,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A343" t="s">
         <v>6</v>
       </c>
@@ -5873,7 +6215,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A344" t="s">
         <v>6</v>
       </c>
@@ -5887,7 +6229,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A345" t="s">
         <v>6</v>
       </c>
@@ -5901,7 +6243,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A346" t="s">
         <v>6</v>
       </c>
@@ -5915,7 +6257,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A347" t="s">
         <v>6</v>
       </c>
@@ -5929,7 +6271,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A348" t="s">
         <v>6</v>
       </c>
@@ -5943,7 +6285,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A349" t="s">
         <v>6</v>
       </c>
@@ -5957,7 +6299,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A350" t="s">
         <v>6</v>
       </c>
@@ -5971,7 +6313,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A351" t="s">
         <v>6</v>
       </c>
@@ -5985,7 +6327,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A352" t="s">
         <v>6</v>
       </c>
@@ -5999,7 +6341,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A353" t="s">
         <v>6</v>
       </c>
@@ -6013,7 +6355,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A354" t="s">
         <v>6</v>
       </c>
@@ -6027,7 +6369,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A355" t="s">
         <v>15</v>
       </c>
@@ -6041,7 +6383,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A356" t="s">
         <v>15</v>
       </c>
@@ -6055,7 +6397,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A357" t="s">
         <v>6</v>
       </c>
@@ -6069,7 +6411,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A358" t="s">
         <v>6</v>
       </c>
@@ -6083,7 +6425,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A359" t="s">
         <v>15</v>
       </c>
@@ -6097,7 +6439,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A360" t="s">
         <v>6</v>
       </c>
@@ -6111,7 +6453,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A361" t="s">
         <v>15</v>
       </c>
@@ -6125,7 +6467,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A362" t="s">
         <v>6</v>
       </c>
@@ -6139,7 +6481,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A363" t="s">
         <v>15</v>
       </c>
@@ -6153,7 +6495,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A364" t="s">
         <v>6</v>
       </c>
@@ -6167,7 +6509,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A365" t="s">
         <v>15</v>
       </c>
@@ -6181,7 +6523,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A366" t="s">
         <v>6</v>
       </c>
@@ -6195,7 +6537,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A367" t="s">
         <v>15</v>
       </c>
@@ -6209,7 +6551,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A368" t="s">
         <v>6</v>
       </c>
@@ -6223,7 +6565,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A369" t="s">
         <v>6</v>
       </c>
@@ -6237,7 +6579,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A370" t="s">
         <v>15</v>
       </c>
@@ -6251,7 +6593,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A371" t="s">
         <v>6</v>
       </c>
@@ -6265,7 +6607,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A372" t="s">
         <v>6</v>
       </c>
@@ -6279,7 +6621,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A373" t="s">
         <v>6</v>
       </c>
@@ -6293,7 +6635,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A374" t="s">
         <v>6</v>
       </c>
@@ -6307,7 +6649,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A375" t="s">
         <v>15</v>
       </c>
@@ -6321,7 +6663,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A376" t="s">
         <v>6</v>
       </c>
@@ -6335,7 +6677,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A377" t="s">
         <v>6</v>
       </c>
@@ -6349,7 +6691,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A378" t="s">
         <v>6</v>
       </c>
@@ -6363,7 +6705,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A379" t="s">
         <v>6</v>
       </c>
@@ -6377,7 +6719,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A380" t="s">
         <v>6</v>
       </c>
@@ -6391,7 +6733,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A381" t="s">
         <v>19</v>
       </c>
@@ -6405,7 +6747,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A382" t="s">
         <v>19</v>
       </c>
@@ -6419,7 +6761,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A383" t="s">
         <v>19</v>
       </c>
@@ -6433,7 +6775,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A384" t="s">
         <v>19</v>
       </c>
@@ -6447,7 +6789,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A385" t="s">
         <v>19</v>
       </c>
@@ -6461,7 +6803,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A386" t="s">
         <v>19</v>
       </c>
@@ -6475,7 +6817,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A387" t="s">
         <v>19</v>
       </c>
@@ -6489,7 +6831,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A388" t="s">
         <v>19</v>
       </c>
@@ -6503,7 +6845,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A389" t="s">
         <v>19</v>
       </c>
@@ -6517,7 +6859,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A390" t="s">
         <v>19</v>
       </c>
@@ -6531,7 +6873,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A391" t="s">
         <v>19</v>
       </c>
@@ -6545,7 +6887,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A392" t="s">
         <v>19</v>
       </c>
@@ -6559,7 +6901,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A393" t="s">
         <v>19</v>
       </c>
@@ -6573,7 +6915,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A394" t="s">
         <v>19</v>
       </c>
@@ -6587,7 +6929,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A395" t="s">
         <v>19</v>
       </c>
@@ -6601,7 +6943,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A396" t="s">
         <v>19</v>
       </c>
@@ -6615,7 +6957,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A397" t="s">
         <v>19</v>
       </c>
@@ -6629,7 +6971,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A398" t="s">
         <v>19</v>
       </c>
@@ -6643,7 +6985,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A399" t="s">
         <v>19</v>
       </c>
@@ -6657,7 +6999,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A400" t="s">
         <v>19</v>
       </c>
@@ -6671,7 +7013,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A401" t="s">
         <v>19</v>
       </c>
@@ -6685,7 +7027,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A402" t="s">
         <v>19</v>
       </c>
@@ -6699,7 +7041,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A403" t="s">
         <v>19</v>
       </c>
@@ -6713,7 +7055,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A404" t="s">
         <v>19</v>
       </c>
@@ -6727,7 +7069,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A405" t="s">
         <v>19</v>
       </c>
@@ -6741,7 +7083,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A406" t="s">
         <v>19</v>
       </c>
@@ -6755,7 +7097,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A407" t="s">
         <v>19</v>
       </c>
@@ -6769,7 +7111,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A408" t="s">
         <v>19</v>
       </c>
@@ -6783,7 +7125,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A409" t="s">
         <v>19</v>
       </c>
@@ -6797,7 +7139,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A410" t="s">
         <v>19</v>
       </c>
@@ -6811,7 +7153,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A411" t="s">
         <v>19</v>
       </c>
@@ -6825,7 +7167,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A412" t="s">
         <v>19</v>
       </c>
@@ -6839,7 +7181,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A413" t="s">
         <v>19</v>
       </c>
@@ -6853,7 +7195,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="414" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A414" t="s">
         <v>19</v>
       </c>
@@ -6867,7 +7209,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A415" t="s">
         <v>19</v>
       </c>
@@ -6881,7 +7223,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A416" t="s">
         <v>19</v>
       </c>
@@ -6895,7 +7237,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A417" t="s">
         <v>19</v>
       </c>
@@ -6909,7 +7251,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A418" t="s">
         <v>19</v>
       </c>
@@ -6923,7 +7265,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A419" t="s">
         <v>19</v>
       </c>
@@ -6937,7 +7279,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A420" t="s">
         <v>19</v>
       </c>
@@ -6951,7 +7293,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A421" t="s">
         <v>19</v>
       </c>
@@ -6965,7 +7307,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A422" t="s">
         <v>19</v>
       </c>
@@ -6979,7 +7321,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A423" t="s">
         <v>19</v>
       </c>
@@ -6993,7 +7335,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A424" t="s">
         <v>19</v>
       </c>
@@ -7007,7 +7349,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A425" t="s">
         <v>19</v>
       </c>
@@ -7021,7 +7363,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A426" t="s">
         <v>19</v>
       </c>
@@ -7035,7 +7377,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="427" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A427" t="s">
         <v>19</v>
       </c>
@@ -7049,7 +7391,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A428" t="s">
         <v>19</v>
       </c>
@@ -7063,7 +7405,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="429" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A429" t="s">
         <v>19</v>
       </c>
@@ -7077,7 +7419,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A430" t="s">
         <v>6</v>
       </c>
@@ -7091,7 +7433,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="431" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A431" t="s">
         <v>19</v>
       </c>
@@ -7105,7 +7447,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A432" t="s">
         <v>6</v>
       </c>
@@ -7119,7 +7461,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A433" t="s">
         <v>19</v>
       </c>
@@ -7133,7 +7475,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A434" t="s">
         <v>6</v>
       </c>
@@ -7147,7 +7489,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A435" t="s">
         <v>19</v>
       </c>
@@ -7161,7 +7503,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="436" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A436" t="s">
         <v>6</v>
       </c>
@@ -7175,7 +7517,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="437" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A437" t="s">
         <v>19</v>
       </c>
@@ -7189,7 +7531,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="438" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A438" t="s">
         <v>6</v>
       </c>
@@ -7203,7 +7545,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="439" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A439" t="s">
         <v>19</v>
       </c>
@@ -7217,7 +7559,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="440" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A440" t="s">
         <v>6</v>
       </c>
@@ -7231,7 +7573,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="441" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A441" t="s">
         <v>19</v>
       </c>
@@ -7245,7 +7587,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="442" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A442" t="s">
         <v>6</v>
       </c>
@@ -7259,7 +7601,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="443" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A443" t="s">
         <v>19</v>
       </c>
@@ -7273,7 +7615,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="444" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A444" t="s">
         <v>6</v>
       </c>
@@ -7287,7 +7629,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="445" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A445" t="s">
         <v>19</v>
       </c>
@@ -7301,7 +7643,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="446" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A446" t="s">
         <v>6</v>
       </c>
@@ -7315,7 +7657,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="447" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A447" t="s">
         <v>19</v>
       </c>
@@ -7329,7 +7671,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="448" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A448" t="s">
         <v>19</v>
       </c>
@@ -7343,7 +7685,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A449" t="s">
         <v>19</v>
       </c>
@@ -7357,7 +7699,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A450" t="s">
         <v>19</v>
       </c>
@@ -7371,7 +7713,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A451" t="s">
         <v>19</v>
       </c>
@@ -7385,7 +7727,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A452" t="s">
         <v>6</v>
       </c>
@@ -7399,7 +7741,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="453" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A453" t="s">
         <v>6</v>
       </c>
@@ -7413,7 +7755,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A454" t="s">
         <v>28</v>
       </c>
@@ -7427,7 +7769,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="455" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A455" t="s">
         <v>28</v>
       </c>
@@ -7441,7 +7783,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A456" t="s">
         <v>28</v>
       </c>
@@ -7455,7 +7797,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="457" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A457" t="s">
         <v>19</v>
       </c>
@@ -7469,7 +7811,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="458" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A458" t="s">
         <v>19</v>
       </c>
@@ -7483,7 +7825,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="459" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A459" t="s">
         <v>19</v>
       </c>
@@ -7497,7 +7839,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="460" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A460" t="s">
         <v>19</v>
       </c>
@@ -7511,7 +7853,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="461" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A461" t="s">
         <v>19</v>
       </c>
@@ -7525,7 +7867,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="462" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A462" t="s">
         <v>19</v>
       </c>
@@ -7539,7 +7881,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="463" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A463" t="s">
         <v>19</v>
       </c>
@@ -7553,7 +7895,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="464" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A464" t="s">
         <v>19</v>
       </c>
@@ -7567,7 +7909,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="465" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A465" t="s">
         <v>28</v>
       </c>
@@ -7581,7 +7923,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A466" t="s">
         <v>6</v>
       </c>
@@ -7595,7 +7937,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="467" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A467" t="s">
         <v>6</v>
       </c>
@@ -7609,7 +7951,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="468" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A468" t="s">
         <v>28</v>
       </c>
@@ -7623,7 +7965,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="469" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A469" t="s">
         <v>28</v>
       </c>
@@ -7637,7 +7979,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="470" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A470" t="s">
         <v>6</v>
       </c>
@@ -7651,7 +7993,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="471" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A471" t="s">
         <v>28</v>
       </c>
@@ -7665,7 +8007,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="472" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A472" t="s">
         <v>28</v>
       </c>
@@ -7679,7 +8021,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A473" t="s">
         <v>6</v>
       </c>
@@ -7693,7 +8035,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="474" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A474" t="s">
         <v>6</v>
       </c>
@@ -7707,7 +8049,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="475" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A475" t="s">
         <v>6</v>
       </c>
@@ -7721,7 +8063,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="476" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A476" t="s">
         <v>6</v>
       </c>
@@ -7735,7 +8077,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="477" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A477" t="s">
         <v>6</v>
       </c>
@@ -7749,7 +8091,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="478" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A478" t="s">
         <v>6</v>
       </c>
@@ -7763,7 +8105,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="479" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A479" t="s">
         <v>6</v>
       </c>
@@ -7777,7 +8119,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A480" t="s">
         <v>6</v>
       </c>
@@ -7791,7 +8133,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="481" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A481" t="s">
         <v>6</v>
       </c>
@@ -7805,7 +8147,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="482" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A482" t="s">
         <v>6</v>
       </c>
@@ -7819,7 +8161,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="483" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A483" t="s">
         <v>6</v>
       </c>
@@ -7833,7 +8175,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="484" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A484" t="s">
         <v>6</v>
       </c>
@@ -7847,7 +8189,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="485" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A485" t="s">
         <v>6</v>
       </c>
@@ -7861,7 +8203,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="486" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A486" t="s">
         <v>15</v>
       </c>
@@ -7875,7 +8217,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A487" t="s">
         <v>6</v>
       </c>
@@ -7889,7 +8231,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A488" t="s">
         <v>6</v>
       </c>
@@ -7903,7 +8245,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A489" t="s">
         <v>6</v>
       </c>
@@ -7917,7 +8259,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="490" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A490" t="s">
         <v>6</v>
       </c>
@@ -7931,7 +8273,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="491" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A491" t="s">
         <v>6</v>
       </c>
@@ -7945,7 +8287,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="492" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A492" t="s">
         <v>6</v>
       </c>
@@ -7959,7 +8301,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="493" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A493" t="s">
         <v>6</v>
       </c>
@@ -7973,7 +8315,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="494" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A494" t="s">
         <v>6</v>
       </c>
@@ -7987,7 +8329,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="495" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A495" t="s">
         <v>6</v>
       </c>
@@ -8001,7 +8343,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="496" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A496" t="s">
         <v>6</v>
       </c>
@@ -8015,7 +8357,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="497" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A497" t="s">
         <v>6</v>
       </c>
@@ -8029,7 +8371,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="498" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A498" t="s">
         <v>6</v>
       </c>
@@ -8043,7 +8385,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="499" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A499" t="s">
         <v>6</v>
       </c>
@@ -8057,7 +8399,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="500" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A500" t="s">
         <v>6</v>
       </c>
@@ -8071,7 +8413,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="501" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A501" t="s">
         <v>6</v>
       </c>
@@ -8085,7 +8427,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="502" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A502" t="s">
         <v>28</v>
       </c>
@@ -8096,10 +8438,10 @@
         <v>248</v>
       </c>
       <c r="D502" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.45">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="503" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A503" t="s">
         <v>28</v>
       </c>
@@ -8110,10 +8452,10 @@
         <v>247</v>
       </c>
       <c r="D503" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.45">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="504" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A504" t="s">
         <v>28</v>
       </c>
@@ -8124,7 +8466,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="505" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A505" t="s">
         <v>6</v>
       </c>
@@ -8132,13 +8474,13 @@
         <v>23660</v>
       </c>
       <c r="C505" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D505" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="506" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A506" t="s">
         <v>6</v>
       </c>
@@ -8146,13 +8488,13 @@
         <v>23661</v>
       </c>
       <c r="C506" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D506" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="507" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A507" t="s">
         <v>6</v>
       </c>
@@ -8160,13 +8502,13 @@
         <v>23649</v>
       </c>
       <c r="C507" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D507" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="508" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A508" t="s">
         <v>6</v>
       </c>
@@ -8174,13 +8516,13 @@
         <v>23650</v>
       </c>
       <c r="C508" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D508" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="509" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A509" t="s">
         <v>6</v>
       </c>
@@ -8191,10 +8533,10 @@
         <v>222</v>
       </c>
       <c r="D509" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.45">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="510" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A510" t="s">
         <v>6</v>
       </c>
@@ -8205,10 +8547,10 @@
         <v>221</v>
       </c>
       <c r="D510" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.45">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A511" t="s">
         <v>6</v>
       </c>
@@ -8216,13 +8558,13 @@
         <v>21863</v>
       </c>
       <c r="C511" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D511" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="512" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A512" t="s">
         <v>6</v>
       </c>
@@ -8230,13 +8572,13 @@
         <v>21864</v>
       </c>
       <c r="C512" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D512" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="513" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A513" t="s">
         <v>6</v>
       </c>
@@ -8244,13 +8586,13 @@
         <v>23728</v>
       </c>
       <c r="C513" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D513" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="514" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A514" t="s">
         <v>6</v>
       </c>
@@ -8258,13 +8600,13 @@
         <v>21865</v>
       </c>
       <c r="C514" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D514" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="515" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A515" t="s">
         <v>6</v>
       </c>
@@ -8272,13 +8614,13 @@
         <v>21866</v>
       </c>
       <c r="C515" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D515" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="516" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A516" t="s">
         <v>6</v>
       </c>
@@ -8286,13 +8628,13 @@
         <v>21867</v>
       </c>
       <c r="C516" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D516" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="517" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A517" t="s">
         <v>6</v>
       </c>
@@ -8300,13 +8642,13 @@
         <v>23974</v>
       </c>
       <c r="C517" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D517" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="518" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A518" t="s">
         <v>6</v>
       </c>
@@ -8314,13 +8656,13 @@
         <v>21868</v>
       </c>
       <c r="C518" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D518" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="519" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A519" t="s">
         <v>6</v>
       </c>
@@ -8328,13 +8670,13 @@
         <v>22053</v>
       </c>
       <c r="C519" t="s">
+        <v>447</v>
+      </c>
+      <c r="D519" t="s">
         <v>448</v>
       </c>
-      <c r="D519" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="520" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A520" t="s">
         <v>6</v>
       </c>
@@ -8342,13 +8684,13 @@
         <v>21869</v>
       </c>
       <c r="C520" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D520" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="521" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A521" t="s">
         <v>6</v>
       </c>
@@ -8356,13 +8698,13 @@
         <v>21870</v>
       </c>
       <c r="C521" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D521" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="522" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A522" t="s">
         <v>6</v>
       </c>
@@ -8370,13 +8712,13 @@
         <v>21871</v>
       </c>
       <c r="C522" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D522" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="523" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A523" t="s">
         <v>6</v>
       </c>
@@ -8384,13 +8726,13 @@
         <v>22048</v>
       </c>
       <c r="C523" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D523" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="524" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A524" t="s">
         <v>6</v>
       </c>
@@ -8398,13 +8740,13 @@
         <v>22049</v>
       </c>
       <c r="C524" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D524" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.45">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="525" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A525" t="s">
         <v>6</v>
       </c>
@@ -8412,13 +8754,13 @@
         <v>21874</v>
       </c>
       <c r="C525" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D525" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="526" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A526" t="s">
         <v>6</v>
       </c>
@@ -8426,13 +8768,13 @@
         <v>21981</v>
       </c>
       <c r="C526" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D526" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.45">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="527" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A527" t="s">
         <v>6</v>
       </c>
@@ -8440,13 +8782,13 @@
         <v>21984</v>
       </c>
       <c r="C527" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D527" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.45">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="528" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A528" t="s">
         <v>6</v>
       </c>
@@ -8454,13 +8796,13 @@
         <v>21873</v>
       </c>
       <c r="C528" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D528" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="529" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A529" t="s">
         <v>6</v>
       </c>
@@ -8468,13 +8810,13 @@
         <v>21872</v>
       </c>
       <c r="C529" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D529" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="530" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A530" t="s">
         <v>6</v>
       </c>
@@ -8482,13 +8824,13 @@
         <v>24649</v>
       </c>
       <c r="C530" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D530" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.45">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="531" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A531" t="s">
         <v>6</v>
       </c>
@@ -8496,13 +8838,13 @@
         <v>21941</v>
       </c>
       <c r="C531" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D531" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.45">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="532" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A532" t="s">
         <v>6</v>
       </c>
@@ -8510,13 +8852,13 @@
         <v>21942</v>
       </c>
       <c r="C532" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D532" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.45">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="533" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A533" t="s">
         <v>6</v>
       </c>
@@ -8524,13 +8866,13 @@
         <v>26701</v>
       </c>
       <c r="C533" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D533" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.45">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="534" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A534" t="s">
         <v>6</v>
       </c>
@@ -8541,10 +8883,10 @@
         <v>233</v>
       </c>
       <c r="D534" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.45">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="535" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A535" t="s">
         <v>6</v>
       </c>
@@ -8555,10 +8897,10 @@
         <v>233</v>
       </c>
       <c r="D535" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.45">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="536" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A536" t="s">
         <v>6</v>
       </c>
@@ -8572,7 +8914,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="537" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A537" t="s">
         <v>6</v>
       </c>
@@ -8583,10 +8925,10 @@
         <v>233</v>
       </c>
       <c r="D537" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.45">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="538" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A538" t="s">
         <v>6</v>
       </c>
@@ -8597,10 +8939,10 @@
         <v>233</v>
       </c>
       <c r="D538" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.45">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="539" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A539" t="s">
         <v>6</v>
       </c>
@@ -8611,10 +8953,10 @@
         <v>233</v>
       </c>
       <c r="D539" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.45">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="540" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A540" t="s">
         <v>6</v>
       </c>
@@ -8625,10 +8967,10 @@
         <v>233</v>
       </c>
       <c r="D540" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.45">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="541" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A541" t="s">
         <v>6</v>
       </c>
@@ -8639,10 +8981,10 @@
         <v>233</v>
       </c>
       <c r="D541" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.45">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="542" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A542" t="s">
         <v>6</v>
       </c>
@@ -8653,10 +8995,10 @@
         <v>233</v>
       </c>
       <c r="D542" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.45">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="543" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A543" t="s">
         <v>6</v>
       </c>
@@ -8667,10 +9009,10 @@
         <v>233</v>
       </c>
       <c r="D543" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.45">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="544" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A544" t="s">
         <v>6</v>
       </c>
@@ -8678,13 +9020,13 @@
         <v>21317</v>
       </c>
       <c r="C544" t="s">
+        <v>463</v>
+      </c>
+      <c r="D544" t="s">
         <v>464</v>
       </c>
-      <c r="D544" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="545" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A545" t="s">
         <v>28</v>
       </c>
@@ -8692,13 +9034,13 @@
         <v>26607</v>
       </c>
       <c r="C545" t="s">
+        <v>465</v>
+      </c>
+      <c r="D545" t="s">
         <v>466</v>
       </c>
-      <c r="D545" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="546" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A546" t="s">
         <v>28</v>
       </c>
@@ -8706,13 +9048,13 @@
         <v>26616</v>
       </c>
       <c r="C546" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D546" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.45">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="547" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A547" t="s">
         <v>28</v>
       </c>
@@ -8723,10 +9065,10 @@
         <v>243</v>
       </c>
       <c r="D547" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.45">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="548" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A548" t="s">
         <v>6</v>
       </c>
@@ -8740,7 +9082,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="549" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="549" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A549" t="s">
         <v>6</v>
       </c>
@@ -8754,7 +9096,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="550" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A550" t="s">
         <v>6</v>
       </c>
@@ -8765,10 +9107,10 @@
         <v>247</v>
       </c>
       <c r="D550" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="551" spans="1:4" x14ac:dyDescent="0.45">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="551" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A551" t="s">
         <v>6</v>
       </c>
@@ -8782,7 +9124,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="552" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A552" t="s">
         <v>6</v>
       </c>
@@ -8796,7 +9138,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="553" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="553" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A553" t="s">
         <v>6</v>
       </c>
@@ -8810,7 +9152,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="554" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="554" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A554" t="s">
         <v>6</v>
       </c>
@@ -8824,7 +9166,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="555" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="555" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A555" t="s">
         <v>6</v>
       </c>
@@ -8835,10 +9177,10 @@
         <v>247</v>
       </c>
       <c r="D555" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="556" spans="1:4" x14ac:dyDescent="0.45">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="556" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A556" t="s">
         <v>6</v>
       </c>
@@ -8849,10 +9191,10 @@
         <v>247</v>
       </c>
       <c r="D556" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="557" spans="1:4" x14ac:dyDescent="0.45">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="557" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A557" t="s">
         <v>6</v>
       </c>
@@ -8866,7 +9208,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="558" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="558" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A558" t="s">
         <v>6</v>
       </c>
@@ -8877,10 +9219,10 @@
         <v>247</v>
       </c>
       <c r="D558" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="559" spans="1:4" x14ac:dyDescent="0.45">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="559" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A559" t="s">
         <v>19</v>
       </c>
@@ -8891,10 +9233,10 @@
         <v>247</v>
       </c>
       <c r="D559" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="560" spans="1:4" x14ac:dyDescent="0.45">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="560" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A560" t="s">
         <v>6</v>
       </c>
@@ -8908,7 +9250,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="561" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A561" t="s">
         <v>6</v>
       </c>
@@ -8919,10 +9261,10 @@
         <v>247</v>
       </c>
       <c r="D561" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.45">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="562" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A562" t="s">
         <v>6</v>
       </c>
@@ -8936,7 +9278,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="563" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A563" t="s">
         <v>6</v>
       </c>
@@ -8950,7 +9292,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="564" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A564" t="s">
         <v>6</v>
       </c>
@@ -8964,7 +9306,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="565" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="565" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A565" t="s">
         <v>6</v>
       </c>
@@ -8978,7 +9320,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="566" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="566" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A566" t="s">
         <v>6</v>
       </c>
@@ -8992,7 +9334,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="567" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A567" t="s">
         <v>6</v>
       </c>
@@ -9006,7 +9348,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="568" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="568" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A568" t="s">
         <v>6</v>
       </c>
@@ -9020,7 +9362,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="569" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="569" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A569" t="s">
         <v>6</v>
       </c>
@@ -9034,7 +9376,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="570" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="570" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A570" t="s">
         <v>6</v>
       </c>
@@ -9048,7 +9390,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="571" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="571" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A571" t="s">
         <v>6</v>
       </c>
@@ -9062,7 +9404,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="572" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="572" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A572" t="s">
         <v>6</v>
       </c>
@@ -9073,10 +9415,10 @@
         <v>247</v>
       </c>
       <c r="D572" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="573" spans="1:4" x14ac:dyDescent="0.45">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="573" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A573" t="s">
         <v>6</v>
       </c>
@@ -9087,10 +9429,10 @@
         <v>247</v>
       </c>
       <c r="D573" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="574" spans="1:4" x14ac:dyDescent="0.45">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="574" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A574" t="s">
         <v>6</v>
       </c>
@@ -9101,10 +9443,10 @@
         <v>247</v>
       </c>
       <c r="D574" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="575" spans="1:4" x14ac:dyDescent="0.45">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="575" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A575" t="s">
         <v>6</v>
       </c>
@@ -9115,10 +9457,10 @@
         <v>247</v>
       </c>
       <c r="D575" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="576" spans="1:4" x14ac:dyDescent="0.45">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="576" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A576" t="s">
         <v>6</v>
       </c>
@@ -9129,10 +9471,10 @@
         <v>247</v>
       </c>
       <c r="D576" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="577" spans="1:4" x14ac:dyDescent="0.45">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="577" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A577" t="s">
         <v>6</v>
       </c>
@@ -9143,10 +9485,10 @@
         <v>247</v>
       </c>
       <c r="D577" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="578" spans="1:4" x14ac:dyDescent="0.45">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="578" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A578" t="s">
         <v>6</v>
       </c>
@@ -9157,10 +9499,10 @@
         <v>247</v>
       </c>
       <c r="D578" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="579" spans="1:4" x14ac:dyDescent="0.45">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="579" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A579" t="s">
         <v>6</v>
       </c>
@@ -9171,10 +9513,10 @@
         <v>247</v>
       </c>
       <c r="D579" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="580" spans="1:4" x14ac:dyDescent="0.45">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="580" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A580" t="s">
         <v>6</v>
       </c>
@@ -9185,10 +9527,10 @@
         <v>247</v>
       </c>
       <c r="D580" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="581" spans="1:4" x14ac:dyDescent="0.45">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="581" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A581" t="s">
         <v>6</v>
       </c>
@@ -9202,7 +9544,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="582" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="582" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A582" t="s">
         <v>6</v>
       </c>
@@ -9216,7 +9558,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="583" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="583" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A583" t="s">
         <v>6</v>
       </c>
@@ -9230,7 +9572,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="584" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="584" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A584" t="s">
         <v>28</v>
       </c>
@@ -9241,10 +9583,10 @@
         <v>247</v>
       </c>
       <c r="D584" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="585" spans="1:4" x14ac:dyDescent="0.45">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="585" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A585" t="s">
         <v>15</v>
       </c>
@@ -9255,7 +9597,1695 @@
         <v>247</v>
       </c>
       <c r="D585" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="586" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A586" t="s">
+        <v>6</v>
+      </c>
+      <c r="B586">
+        <v>21863</v>
+      </c>
+      <c r="C586" t="s">
         <v>485</v>
+      </c>
+      <c r="D586" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="587" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A587" t="s">
+        <v>6</v>
+      </c>
+      <c r="B587">
+        <v>21864</v>
+      </c>
+      <c r="C587" t="s">
+        <v>485</v>
+      </c>
+      <c r="D587" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="588" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A588" t="s">
+        <v>6</v>
+      </c>
+      <c r="B588">
+        <v>21866</v>
+      </c>
+      <c r="C588" t="s">
+        <v>485</v>
+      </c>
+      <c r="D588" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="589" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A589" t="s">
+        <v>6</v>
+      </c>
+      <c r="B589">
+        <v>21867</v>
+      </c>
+      <c r="C589" t="s">
+        <v>485</v>
+      </c>
+      <c r="D589" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="590" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A590" t="s">
+        <v>6</v>
+      </c>
+      <c r="B590">
+        <v>23974</v>
+      </c>
+      <c r="C590" t="s">
+        <v>485</v>
+      </c>
+      <c r="D590" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="591" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A591" t="s">
+        <v>6</v>
+      </c>
+      <c r="B591">
+        <v>21868</v>
+      </c>
+      <c r="C591" t="s">
+        <v>485</v>
+      </c>
+      <c r="D591" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="592" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A592" t="s">
+        <v>6</v>
+      </c>
+      <c r="B592">
+        <v>22053</v>
+      </c>
+      <c r="C592" t="s">
+        <v>485</v>
+      </c>
+      <c r="D592" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="593" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A593" t="s">
+        <v>6</v>
+      </c>
+      <c r="B593">
+        <v>21874</v>
+      </c>
+      <c r="C593" t="s">
+        <v>485</v>
+      </c>
+      <c r="D593" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="594" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A594" t="s">
+        <v>6</v>
+      </c>
+      <c r="B594">
+        <v>21981</v>
+      </c>
+      <c r="C594" t="s">
+        <v>485</v>
+      </c>
+      <c r="D594" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="595" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A595" t="s">
+        <v>6</v>
+      </c>
+      <c r="B595">
+        <v>21873</v>
+      </c>
+      <c r="C595" t="s">
+        <v>485</v>
+      </c>
+      <c r="D595" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="596" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A596" t="s">
+        <v>6</v>
+      </c>
+      <c r="B596">
+        <v>21872</v>
+      </c>
+      <c r="C596" t="s">
+        <v>485</v>
+      </c>
+      <c r="D596" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="597" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A597" t="s">
+        <v>6</v>
+      </c>
+      <c r="B597">
+        <v>22084</v>
+      </c>
+      <c r="C597" t="s">
+        <v>486</v>
+      </c>
+      <c r="D597" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="598" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A598" t="s">
+        <v>6</v>
+      </c>
+      <c r="B598">
+        <v>22085</v>
+      </c>
+      <c r="C598" t="s">
+        <v>486</v>
+      </c>
+      <c r="D598" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="599" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A599" t="s">
+        <v>15</v>
+      </c>
+      <c r="B599">
+        <v>26612</v>
+      </c>
+      <c r="C599" t="s">
+        <v>486</v>
+      </c>
+      <c r="D599" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="600" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A600" t="s">
+        <v>15</v>
+      </c>
+      <c r="B600">
+        <v>20932</v>
+      </c>
+      <c r="C600" t="s">
+        <v>486</v>
+      </c>
+      <c r="D600" t="s">
+        <v>488</v>
+      </c>
+      <c r="E600" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="601" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A601" t="s">
+        <v>6</v>
+      </c>
+      <c r="B601">
+        <v>26734</v>
+      </c>
+      <c r="C601" t="s">
+        <v>447</v>
+      </c>
+      <c r="D601" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="602" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A602" t="s">
+        <v>6</v>
+      </c>
+      <c r="B602">
+        <v>23718</v>
+      </c>
+      <c r="C602" t="s">
+        <v>447</v>
+      </c>
+      <c r="D602" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="603" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A603" t="s">
+        <v>6</v>
+      </c>
+      <c r="B603">
+        <v>23719</v>
+      </c>
+      <c r="C603" t="s">
+        <v>447</v>
+      </c>
+      <c r="D603" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="604" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A604" t="s">
+        <v>6</v>
+      </c>
+      <c r="B604">
+        <v>23723</v>
+      </c>
+      <c r="C604" t="s">
+        <v>447</v>
+      </c>
+      <c r="D604" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="605" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A605" t="s">
+        <v>6</v>
+      </c>
+      <c r="B605">
+        <v>23722</v>
+      </c>
+      <c r="C605" t="s">
+        <v>447</v>
+      </c>
+      <c r="D605" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="606" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A606" t="s">
+        <v>6</v>
+      </c>
+      <c r="B606">
+        <v>23721</v>
+      </c>
+      <c r="C606" t="s">
+        <v>447</v>
+      </c>
+      <c r="D606" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="607" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A607" t="s">
+        <v>6</v>
+      </c>
+      <c r="B607">
+        <v>23720</v>
+      </c>
+      <c r="C607" t="s">
+        <v>447</v>
+      </c>
+      <c r="D607" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="608" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A608" t="s">
+        <v>6</v>
+      </c>
+      <c r="B608">
+        <v>23724</v>
+      </c>
+      <c r="C608" t="s">
+        <v>447</v>
+      </c>
+      <c r="D608" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="609" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A609" t="s">
+        <v>6</v>
+      </c>
+      <c r="B609">
+        <v>23725</v>
+      </c>
+      <c r="C609" t="s">
+        <v>447</v>
+      </c>
+      <c r="D609" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="610" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A610" t="s">
+        <v>6</v>
+      </c>
+      <c r="B610">
+        <v>23726</v>
+      </c>
+      <c r="C610" t="s">
+        <v>447</v>
+      </c>
+      <c r="D610" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="611" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A611" t="s">
+        <v>6</v>
+      </c>
+      <c r="B611">
+        <v>23727</v>
+      </c>
+      <c r="C611" t="s">
+        <v>447</v>
+      </c>
+      <c r="D611" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="612" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A612" t="s">
+        <v>6</v>
+      </c>
+      <c r="B612">
+        <v>22074</v>
+      </c>
+      <c r="C612" t="s">
+        <v>447</v>
+      </c>
+      <c r="D612" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="613" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A613" t="s">
+        <v>6</v>
+      </c>
+      <c r="B613">
+        <v>22075</v>
+      </c>
+      <c r="C613" t="s">
+        <v>447</v>
+      </c>
+      <c r="D613" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="614" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A614" t="s">
+        <v>6</v>
+      </c>
+      <c r="B614">
+        <v>22076</v>
+      </c>
+      <c r="C614" t="s">
+        <v>447</v>
+      </c>
+      <c r="D614" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="615" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A615" t="s">
+        <v>6</v>
+      </c>
+      <c r="B615">
+        <v>23729</v>
+      </c>
+      <c r="C615" t="s">
+        <v>447</v>
+      </c>
+      <c r="D615" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="616" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A616" t="s">
+        <v>6</v>
+      </c>
+      <c r="B616">
+        <v>22078</v>
+      </c>
+      <c r="C616" t="s">
+        <v>447</v>
+      </c>
+      <c r="D616" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="617" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A617" t="s">
+        <v>6</v>
+      </c>
+      <c r="B617">
+        <v>22079</v>
+      </c>
+      <c r="C617" t="s">
+        <v>447</v>
+      </c>
+      <c r="D617" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="618" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A618" t="s">
+        <v>6</v>
+      </c>
+      <c r="B618">
+        <v>23975</v>
+      </c>
+      <c r="C618" t="s">
+        <v>447</v>
+      </c>
+      <c r="D618" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="619" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A619" t="s">
+        <v>6</v>
+      </c>
+      <c r="B619">
+        <v>22080</v>
+      </c>
+      <c r="C619" t="s">
+        <v>447</v>
+      </c>
+      <c r="D619" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="620" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A620" t="s">
+        <v>6</v>
+      </c>
+      <c r="B620">
+        <v>22081</v>
+      </c>
+      <c r="C620" t="s">
+        <v>447</v>
+      </c>
+      <c r="D620" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="621" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A621" t="s">
+        <v>6</v>
+      </c>
+      <c r="B621">
+        <v>22082</v>
+      </c>
+      <c r="C621" t="s">
+        <v>447</v>
+      </c>
+      <c r="D621" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="622" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A622" t="s">
+        <v>6</v>
+      </c>
+      <c r="B622">
+        <v>22785</v>
+      </c>
+      <c r="C622" t="s">
+        <v>247</v>
+      </c>
+      <c r="D622" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="623" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A623" t="s">
+        <v>6</v>
+      </c>
+      <c r="B623">
+        <v>22806</v>
+      </c>
+      <c r="C623" t="s">
+        <v>247</v>
+      </c>
+      <c r="D623" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="624" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A624" t="s">
+        <v>6</v>
+      </c>
+      <c r="B624">
+        <v>23615</v>
+      </c>
+      <c r="C624" t="s">
+        <v>247</v>
+      </c>
+      <c r="D624" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="625" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A625" t="s">
+        <v>6</v>
+      </c>
+      <c r="B625">
+        <v>24348</v>
+      </c>
+      <c r="C625" t="s">
+        <v>247</v>
+      </c>
+      <c r="D625" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="626" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A626" t="s">
+        <v>15</v>
+      </c>
+      <c r="B626">
+        <v>24936</v>
+      </c>
+      <c r="C626" t="s">
+        <v>247</v>
+      </c>
+      <c r="D626" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="627" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A627" t="s">
+        <v>6</v>
+      </c>
+      <c r="B627">
+        <v>23176</v>
+      </c>
+      <c r="C627" t="s">
+        <v>247</v>
+      </c>
+      <c r="D627" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="628" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A628" t="s">
+        <v>6</v>
+      </c>
+      <c r="B628">
+        <v>25030</v>
+      </c>
+      <c r="C628" t="s">
+        <v>247</v>
+      </c>
+      <c r="D628" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="629" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A629" t="s">
+        <v>15</v>
+      </c>
+      <c r="B629">
+        <v>24935</v>
+      </c>
+      <c r="C629" t="s">
+        <v>252</v>
+      </c>
+      <c r="D629" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="630" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A630" t="s">
+        <v>6</v>
+      </c>
+      <c r="B630">
+        <v>24990</v>
+      </c>
+      <c r="C630" t="s">
+        <v>252</v>
+      </c>
+      <c r="D630" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="631" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A631" t="s">
+        <v>15</v>
+      </c>
+      <c r="B631">
+        <v>24932</v>
+      </c>
+      <c r="C631" t="s">
+        <v>223</v>
+      </c>
+      <c r="D631" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="632" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A632" t="s">
+        <v>15</v>
+      </c>
+      <c r="B632">
+        <v>22378</v>
+      </c>
+      <c r="D632" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="633" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A633" t="s">
+        <v>15</v>
+      </c>
+      <c r="B633">
+        <v>22380</v>
+      </c>
+      <c r="D633" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="634" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A634" t="s">
+        <v>6</v>
+      </c>
+      <c r="B634">
+        <v>22310</v>
+      </c>
+      <c r="C634" t="s">
+        <v>223</v>
+      </c>
+      <c r="D634" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="635" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A635" t="s">
+        <v>6</v>
+      </c>
+      <c r="B635">
+        <v>26720</v>
+      </c>
+      <c r="D635" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="636" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A636" t="s">
+        <v>6</v>
+      </c>
+      <c r="B636">
+        <v>22312</v>
+      </c>
+      <c r="C636" t="s">
+        <v>221</v>
+      </c>
+      <c r="D636" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="637" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A637" t="s">
+        <v>28</v>
+      </c>
+      <c r="B637">
+        <v>21222</v>
+      </c>
+      <c r="C637" t="s">
+        <v>222</v>
+      </c>
+      <c r="D637" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="638" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A638" t="s">
+        <v>6</v>
+      </c>
+      <c r="B638">
+        <v>22563</v>
+      </c>
+      <c r="C638" t="s">
+        <v>233</v>
+      </c>
+      <c r="D638" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="639" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A639" t="s">
+        <v>28</v>
+      </c>
+      <c r="B639">
+        <v>21337</v>
+      </c>
+      <c r="C639" t="s">
+        <v>233</v>
+      </c>
+      <c r="D639" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="640" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A640" t="s">
+        <v>6</v>
+      </c>
+      <c r="B640">
+        <v>22567</v>
+      </c>
+      <c r="C640" t="s">
+        <v>235</v>
+      </c>
+      <c r="D640" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="641" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A641" t="s">
+        <v>6</v>
+      </c>
+      <c r="B641">
+        <v>21423</v>
+      </c>
+      <c r="C641" t="s">
+        <v>235</v>
+      </c>
+      <c r="D641" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="642" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A642" t="s">
+        <v>6</v>
+      </c>
+      <c r="B642">
+        <v>21418</v>
+      </c>
+      <c r="C642" t="s">
+        <v>235</v>
+      </c>
+      <c r="D642" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="643" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A643" t="s">
+        <v>6</v>
+      </c>
+      <c r="B643">
+        <v>21417</v>
+      </c>
+      <c r="C643" t="s">
+        <v>235</v>
+      </c>
+      <c r="D643" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="644" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A644" t="s">
+        <v>6</v>
+      </c>
+      <c r="B644">
+        <v>21416</v>
+      </c>
+      <c r="C644" t="s">
+        <v>235</v>
+      </c>
+      <c r="D644" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="645" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A645" t="s">
+        <v>6</v>
+      </c>
+      <c r="B645">
+        <v>22576</v>
+      </c>
+      <c r="C645" t="s">
+        <v>235</v>
+      </c>
+      <c r="D645" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="646" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A646" t="s">
+        <v>6</v>
+      </c>
+      <c r="B646">
+        <v>22578</v>
+      </c>
+      <c r="C646" t="s">
+        <v>235</v>
+      </c>
+      <c r="D646" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="647" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A647" t="s">
+        <v>6</v>
+      </c>
+      <c r="B647">
+        <v>22577</v>
+      </c>
+      <c r="C647" t="s">
+        <v>235</v>
+      </c>
+      <c r="D647" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="648" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A648" t="s">
+        <v>6</v>
+      </c>
+      <c r="B648">
+        <v>22568</v>
+      </c>
+      <c r="C648" t="s">
+        <v>235</v>
+      </c>
+      <c r="D648" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="649" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A649" t="s">
+        <v>6</v>
+      </c>
+      <c r="B649">
+        <v>22569</v>
+      </c>
+      <c r="C649" t="s">
+        <v>235</v>
+      </c>
+      <c r="D649" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="650" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A650" t="s">
+        <v>6</v>
+      </c>
+      <c r="B650">
+        <v>22570</v>
+      </c>
+      <c r="C650" t="s">
+        <v>235</v>
+      </c>
+      <c r="D650" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="651" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A651" t="s">
+        <v>6</v>
+      </c>
+      <c r="B651">
+        <v>26600</v>
+      </c>
+      <c r="C651" t="s">
+        <v>235</v>
+      </c>
+      <c r="D651" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="652" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A652" t="s">
+        <v>6</v>
+      </c>
+      <c r="B652">
+        <v>22571</v>
+      </c>
+      <c r="C652" t="s">
+        <v>235</v>
+      </c>
+      <c r="D652" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="653" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A653" t="s">
+        <v>6</v>
+      </c>
+      <c r="B653">
+        <v>22572</v>
+      </c>
+      <c r="C653" t="s">
+        <v>235</v>
+      </c>
+      <c r="D653" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="654" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A654" t="s">
+        <v>6</v>
+      </c>
+      <c r="B654">
+        <v>22522</v>
+      </c>
+      <c r="C654" t="s">
+        <v>235</v>
+      </c>
+      <c r="D654" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="655" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A655" t="s">
+        <v>6</v>
+      </c>
+      <c r="B655">
+        <v>22566</v>
+      </c>
+      <c r="C655" t="s">
+        <v>235</v>
+      </c>
+      <c r="D655" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="656" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A656" t="s">
+        <v>28</v>
+      </c>
+      <c r="B656">
+        <v>21419</v>
+      </c>
+      <c r="C656" t="s">
+        <v>235</v>
+      </c>
+      <c r="D656" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="657" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A657" t="s">
+        <v>6</v>
+      </c>
+      <c r="B657">
+        <v>26722</v>
+      </c>
+      <c r="C657" t="s">
+        <v>237</v>
+      </c>
+      <c r="D657" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="658" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A658" t="s">
+        <v>6</v>
+      </c>
+      <c r="B658">
+        <v>24747</v>
+      </c>
+      <c r="C658" t="s">
+        <v>237</v>
+      </c>
+      <c r="D658" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="659" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A659" t="s">
+        <v>15</v>
+      </c>
+      <c r="B659">
+        <v>24965</v>
+      </c>
+      <c r="C659" t="s">
+        <v>237</v>
+      </c>
+      <c r="D659" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="660" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A660" t="s">
+        <v>6</v>
+      </c>
+      <c r="B660">
+        <v>24975</v>
+      </c>
+      <c r="C660" t="s">
+        <v>237</v>
+      </c>
+      <c r="D660" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="661" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A661" t="s">
+        <v>15</v>
+      </c>
+      <c r="B661">
+        <v>24966</v>
+      </c>
+      <c r="C661" t="s">
+        <v>237</v>
+      </c>
+      <c r="D661" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="662" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A662" t="s">
+        <v>6</v>
+      </c>
+      <c r="B662">
+        <v>24976</v>
+      </c>
+      <c r="C662" t="s">
+        <v>237</v>
+      </c>
+      <c r="D662" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="663" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A663" t="s">
+        <v>15</v>
+      </c>
+      <c r="B663">
+        <v>24967</v>
+      </c>
+      <c r="C663" t="s">
+        <v>237</v>
+      </c>
+      <c r="D663" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="664" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A664" t="s">
+        <v>6</v>
+      </c>
+      <c r="B664">
+        <v>24977</v>
+      </c>
+      <c r="C664" t="s">
+        <v>237</v>
+      </c>
+      <c r="D664" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="665" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A665" t="s">
+        <v>15</v>
+      </c>
+      <c r="B665">
+        <v>24968</v>
+      </c>
+      <c r="C665" t="s">
+        <v>237</v>
+      </c>
+      <c r="D665" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="666" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A666" t="s">
+        <v>6</v>
+      </c>
+      <c r="B666">
+        <v>24978</v>
+      </c>
+      <c r="C666" t="s">
+        <v>237</v>
+      </c>
+      <c r="D666" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="667" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A667" t="s">
+        <v>15</v>
+      </c>
+      <c r="B667">
+        <v>24931</v>
+      </c>
+      <c r="C667" t="s">
+        <v>237</v>
+      </c>
+      <c r="D667" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="668" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A668" t="s">
+        <v>6</v>
+      </c>
+      <c r="B668">
+        <v>24979</v>
+      </c>
+      <c r="C668" t="s">
+        <v>237</v>
+      </c>
+      <c r="D668" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="669" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A669" t="s">
+        <v>15</v>
+      </c>
+      <c r="B669">
+        <v>24969</v>
+      </c>
+      <c r="C669" t="s">
+        <v>237</v>
+      </c>
+      <c r="D669" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="670" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A670" t="s">
+        <v>6</v>
+      </c>
+      <c r="B670">
+        <v>24980</v>
+      </c>
+      <c r="C670" t="s">
+        <v>237</v>
+      </c>
+      <c r="D670" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="671" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A671" t="s">
+        <v>15</v>
+      </c>
+      <c r="B671">
+        <v>24970</v>
+      </c>
+      <c r="C671" t="s">
+        <v>237</v>
+      </c>
+      <c r="D671" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="672" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A672" t="s">
+        <v>6</v>
+      </c>
+      <c r="B672">
+        <v>24981</v>
+      </c>
+      <c r="C672" t="s">
+        <v>237</v>
+      </c>
+      <c r="D672" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="673" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A673" t="s">
+        <v>15</v>
+      </c>
+      <c r="B673">
+        <v>24971</v>
+      </c>
+      <c r="C673" t="s">
+        <v>237</v>
+      </c>
+      <c r="D673" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="674" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A674" t="s">
+        <v>6</v>
+      </c>
+      <c r="B674">
+        <v>24982</v>
+      </c>
+      <c r="C674" t="s">
+        <v>237</v>
+      </c>
+      <c r="D674" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="675" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A675" t="s">
+        <v>15</v>
+      </c>
+      <c r="B675">
+        <v>24972</v>
+      </c>
+      <c r="C675" t="s">
+        <v>237</v>
+      </c>
+      <c r="D675" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="676" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A676" t="s">
+        <v>6</v>
+      </c>
+      <c r="B676">
+        <v>24983</v>
+      </c>
+      <c r="C676" t="s">
+        <v>237</v>
+      </c>
+      <c r="D676" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="677" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A677" t="s">
+        <v>28</v>
+      </c>
+      <c r="B677">
+        <v>21211</v>
+      </c>
+      <c r="C677" t="s">
+        <v>237</v>
+      </c>
+      <c r="D677" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="678" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A678" t="s">
+        <v>6</v>
+      </c>
+      <c r="B678">
+        <v>22715</v>
+      </c>
+      <c r="C678" t="s">
+        <v>240</v>
+      </c>
+      <c r="D678" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="679" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A679" t="s">
+        <v>6</v>
+      </c>
+      <c r="B679">
+        <v>22717</v>
+      </c>
+      <c r="C679" t="s">
+        <v>240</v>
+      </c>
+      <c r="D679" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="680" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A680" t="s">
+        <v>6</v>
+      </c>
+      <c r="B680">
+        <v>22739</v>
+      </c>
+      <c r="C680" t="s">
+        <v>240</v>
+      </c>
+      <c r="D680" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="681" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A681" t="s">
+        <v>6</v>
+      </c>
+      <c r="B681">
+        <v>22719</v>
+      </c>
+      <c r="C681" t="s">
+        <v>240</v>
+      </c>
+      <c r="D681" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="682" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A682" t="s">
+        <v>6</v>
+      </c>
+      <c r="B682">
+        <v>22731</v>
+      </c>
+      <c r="C682" t="s">
+        <v>240</v>
+      </c>
+      <c r="D682" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="683" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A683" t="s">
+        <v>6</v>
+      </c>
+      <c r="B683">
+        <v>22735</v>
+      </c>
+      <c r="C683" t="s">
+        <v>240</v>
+      </c>
+      <c r="D683" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="684" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A684" t="s">
+        <v>6</v>
+      </c>
+      <c r="B684">
+        <v>22732</v>
+      </c>
+      <c r="C684" t="s">
+        <v>240</v>
+      </c>
+      <c r="D684" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="685" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A685" t="s">
+        <v>6</v>
+      </c>
+      <c r="B685">
+        <v>22736</v>
+      </c>
+      <c r="C685" t="s">
+        <v>240</v>
+      </c>
+      <c r="D685" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="686" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A686" t="s">
+        <v>6</v>
+      </c>
+      <c r="B686">
+        <v>22733</v>
+      </c>
+      <c r="C686" t="s">
+        <v>240</v>
+      </c>
+      <c r="D686" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="687" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A687" t="s">
+        <v>6</v>
+      </c>
+      <c r="B687">
+        <v>22737</v>
+      </c>
+      <c r="C687" t="s">
+        <v>240</v>
+      </c>
+      <c r="D687" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="688" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A688" t="s">
+        <v>6</v>
+      </c>
+      <c r="B688">
+        <v>22734</v>
+      </c>
+      <c r="C688" t="s">
+        <v>240</v>
+      </c>
+      <c r="D688" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="689" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A689" t="s">
+        <v>6</v>
+      </c>
+      <c r="B689">
+        <v>22738</v>
+      </c>
+      <c r="C689" t="s">
+        <v>240</v>
+      </c>
+      <c r="D689" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="690" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A690" t="s">
+        <v>28</v>
+      </c>
+      <c r="B690">
+        <v>21573</v>
+      </c>
+      <c r="C690" t="s">
+        <v>240</v>
+      </c>
+      <c r="D690" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="691" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A691" t="s">
+        <v>28</v>
+      </c>
+      <c r="B691">
+        <v>21574</v>
+      </c>
+      <c r="C691" t="s">
+        <v>240</v>
+      </c>
+      <c r="D691" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="692" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A692" t="s">
+        <v>6</v>
+      </c>
+      <c r="B692">
+        <v>22729</v>
+      </c>
+      <c r="C692" t="s">
+        <v>240</v>
+      </c>
+      <c r="D692" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="693" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A693" t="s">
+        <v>6</v>
+      </c>
+      <c r="B693">
+        <v>22730</v>
+      </c>
+      <c r="C693" t="s">
+        <v>240</v>
+      </c>
+      <c r="D693" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="694" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A694" t="s">
+        <v>6</v>
+      </c>
+      <c r="B694">
+        <v>22727</v>
+      </c>
+      <c r="C694" t="s">
+        <v>240</v>
+      </c>
+      <c r="D694" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="695" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A695" t="s">
+        <v>6</v>
+      </c>
+      <c r="B695">
+        <v>22728</v>
+      </c>
+      <c r="C695" t="s">
+        <v>240</v>
+      </c>
+      <c r="D695" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="696" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A696" t="s">
+        <v>6</v>
+      </c>
+      <c r="B696">
+        <v>22488</v>
+      </c>
+      <c r="C696" t="s">
+        <v>241</v>
+      </c>
+      <c r="D696" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="697" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A697" t="s">
+        <v>6</v>
+      </c>
+      <c r="B697">
+        <v>22489</v>
+      </c>
+      <c r="C697" t="s">
+        <v>241</v>
+      </c>
+      <c r="D697" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="698" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A698" t="s">
+        <v>6</v>
+      </c>
+      <c r="B698">
+        <v>22490</v>
+      </c>
+      <c r="C698" t="s">
+        <v>241</v>
+      </c>
+      <c r="D698" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="699" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A699" t="s">
+        <v>6</v>
+      </c>
+      <c r="B699">
+        <v>22492</v>
+      </c>
+      <c r="C699" t="s">
+        <v>241</v>
+      </c>
+      <c r="D699" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="700" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A700" t="s">
+        <v>6</v>
+      </c>
+      <c r="B700">
+        <v>22491</v>
+      </c>
+      <c r="C700" t="s">
+        <v>241</v>
+      </c>
+      <c r="D700" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="701" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A701" t="s">
+        <v>28</v>
+      </c>
+      <c r="B701">
+        <v>21217</v>
+      </c>
+      <c r="C701" t="s">
+        <v>241</v>
+      </c>
+      <c r="D701" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="702" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A702" t="s">
+        <v>28</v>
+      </c>
+      <c r="B702">
+        <v>21216</v>
+      </c>
+      <c r="C702" t="s">
+        <v>241</v>
+      </c>
+      <c r="D702" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="703" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A703" t="s">
+        <v>28</v>
+      </c>
+      <c r="B703">
+        <v>21547</v>
+      </c>
+      <c r="C703" t="s">
+        <v>248</v>
+      </c>
+      <c r="D703" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="704" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A704" t="s">
+        <v>6</v>
+      </c>
+      <c r="B704">
+        <v>23238</v>
+      </c>
+      <c r="C704" t="s">
+        <v>250</v>
+      </c>
+      <c r="D704" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="705" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A705" t="s">
+        <v>6</v>
+      </c>
+      <c r="B705">
+        <v>23236</v>
+      </c>
+      <c r="C705" t="s">
+        <v>250</v>
+      </c>
+      <c r="D705" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="706" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A706" t="s">
+        <v>6</v>
+      </c>
+      <c r="B706">
+        <v>23266</v>
+      </c>
+      <c r="C706" t="s">
+        <v>250</v>
+      </c>
+      <c r="D706" t="s">
+        <v>537</v>
       </c>
     </row>
   </sheetData>

--- a/Files/Controls.xlsx
+++ b/Files/Controls.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Otto\Dokument\src\VismaAdministration-NVDAAddOn\Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\NVDA\VismaAdministration\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D8BE0A-98D9-459D-840A-099BEC45595A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D8B9246-DD08-4391-A200-437D5C9D8CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2470" yWindow="2470" windowWidth="14400" windowHeight="7290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1425" yWindow="1425" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1907" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1919" uniqueCount="540">
   <si>
     <t>WindowClassName</t>
   </si>
@@ -1647,6 +1647,12 @@
   </si>
   <si>
     <t>Skuldkonto</t>
+  </si>
+  <si>
+    <t>Aktivering av programvaran</t>
+  </si>
+  <si>
+    <t>Lösenord</t>
   </si>
 </sst>
 </file>
@@ -1691,74 +1697,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1775,10 +1713,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="3D3D3D"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFAEF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -2033,14 +1971,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E706"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A1:E710"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="26.04296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="44.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2057,7 +1995,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -2071,7 +2009,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -2085,7 +2023,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -2099,7 +2037,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -2113,7 +2051,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -2127,7 +2065,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -2141,7 +2079,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -2155,7 +2093,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -2169,7 +2107,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -2183,7 +2121,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -2197,7 +2135,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -2211,7 +2149,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -2225,7 +2163,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -2239,7 +2177,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -2253,7 +2191,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -2267,7 +2205,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -2281,7 +2219,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -2295,7 +2233,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -2309,7 +2247,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -2323,7 +2261,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -2337,7 +2275,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -2351,7 +2289,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -2365,7 +2303,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -2382,7 +2320,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -2396,7 +2334,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -2410,7 +2348,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -2421,7 +2359,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -2432,7 +2370,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -2443,7 +2381,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -2454,7 +2392,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>28</v>
       </c>
@@ -2468,7 +2406,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>3</v>
       </c>
@@ -2479,7 +2417,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -2493,7 +2431,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -2504,7 +2442,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -2515,7 +2453,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -2526,7 +2464,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -2537,7 +2475,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -2548,7 +2486,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -2559,7 +2497,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -2570,7 +2508,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>15</v>
       </c>
@@ -2581,7 +2519,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -2592,7 +2530,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -2603,7 +2541,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>19</v>
       </c>
@@ -2614,7 +2552,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>19</v>
       </c>
@@ -2625,7 +2563,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -2636,7 +2574,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>19</v>
       </c>
@@ -2647,7 +2585,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>19</v>
       </c>
@@ -2658,7 +2596,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -2669,7 +2607,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -2680,7 +2618,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -2691,7 +2629,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>6</v>
       </c>
@@ -2702,7 +2640,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>6</v>
       </c>
@@ -2716,7 +2654,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>6</v>
       </c>
@@ -2727,7 +2665,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -2738,7 +2676,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>6</v>
       </c>
@@ -2749,7 +2687,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>6</v>
       </c>
@@ -2760,7 +2698,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>19</v>
       </c>
@@ -2771,7 +2709,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -2785,7 +2723,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>6</v>
       </c>
@@ -2796,7 +2734,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>6</v>
       </c>
@@ -2807,7 +2745,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>6</v>
       </c>
@@ -2818,7 +2756,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>6</v>
       </c>
@@ -2829,7 +2767,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>6</v>
       </c>
@@ -2840,7 +2778,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>6</v>
       </c>
@@ -2851,7 +2789,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>6</v>
       </c>
@@ -2862,7 +2800,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>15</v>
       </c>
@@ -2876,7 +2814,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>6</v>
       </c>
@@ -2893,7 +2831,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -2907,7 +2845,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>6</v>
       </c>
@@ -2918,7 +2856,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>6</v>
       </c>
@@ -2929,7 +2867,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>6</v>
       </c>
@@ -2940,7 +2878,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>6</v>
       </c>
@@ -2951,7 +2889,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>6</v>
       </c>
@@ -2962,7 +2900,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>6</v>
       </c>
@@ -2973,7 +2911,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>6</v>
       </c>
@@ -2984,7 +2922,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>6</v>
       </c>
@@ -2995,7 +2933,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>6</v>
       </c>
@@ -3006,7 +2944,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>6</v>
       </c>
@@ -3017,7 +2955,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>6</v>
       </c>
@@ -3028,7 +2966,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>6</v>
       </c>
@@ -3039,7 +2977,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>6</v>
       </c>
@@ -3053,7 +2991,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>6</v>
       </c>
@@ -3067,7 +3005,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>6</v>
       </c>
@@ -3081,7 +3019,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>6</v>
       </c>
@@ -3095,7 +3033,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>6</v>
       </c>
@@ -3109,7 +3047,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>6</v>
       </c>
@@ -3123,7 +3061,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>6</v>
       </c>
@@ -3134,7 +3072,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>6</v>
       </c>
@@ -3145,7 +3083,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>6</v>
       </c>
@@ -3156,7 +3094,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>6</v>
       </c>
@@ -3167,7 +3105,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>6</v>
       </c>
@@ -3178,7 +3116,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>6</v>
       </c>
@@ -3189,7 +3127,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>19</v>
       </c>
@@ -3200,7 +3138,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>6</v>
       </c>
@@ -3211,7 +3149,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>19</v>
       </c>
@@ -3222,7 +3160,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>19</v>
       </c>
@@ -3233,7 +3171,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>19</v>
       </c>
@@ -3244,7 +3182,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>19</v>
       </c>
@@ -3255,7 +3193,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>19</v>
       </c>
@@ -3269,7 +3207,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>19</v>
       </c>
@@ -3283,7 +3221,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>19</v>
       </c>
@@ -3294,7 +3232,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>19</v>
       </c>
@@ -3305,7 +3243,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>19</v>
       </c>
@@ -3316,7 +3254,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>19</v>
       </c>
@@ -3327,7 +3265,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>15</v>
       </c>
@@ -3341,7 +3279,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>15</v>
       </c>
@@ -3355,7 +3293,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>15</v>
       </c>
@@ -3366,7 +3304,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>6</v>
       </c>
@@ -3380,7 +3318,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>6</v>
       </c>
@@ -3391,7 +3329,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>6</v>
       </c>
@@ -3402,7 +3340,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>6</v>
       </c>
@@ -3413,7 +3351,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>6</v>
       </c>
@@ -3424,7 +3362,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>6</v>
       </c>
@@ -3435,7 +3373,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>6</v>
       </c>
@@ -3446,7 +3384,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>6</v>
       </c>
@@ -3457,7 +3395,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>6</v>
       </c>
@@ -3468,7 +3406,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>6</v>
       </c>
@@ -3479,7 +3417,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>6</v>
       </c>
@@ -3490,7 +3428,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>6</v>
       </c>
@@ -3501,7 +3439,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>6</v>
       </c>
@@ -3512,7 +3450,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>6</v>
       </c>
@@ -3523,7 +3461,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>6</v>
       </c>
@@ -3534,7 +3472,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>6</v>
       </c>
@@ -3545,7 +3483,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>6</v>
       </c>
@@ -3556,7 +3494,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>6</v>
       </c>
@@ -3567,7 +3505,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>6</v>
       </c>
@@ -3578,7 +3516,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>6</v>
       </c>
@@ -3589,7 +3527,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>6</v>
       </c>
@@ -3600,7 +3538,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>6</v>
       </c>
@@ -3611,7 +3549,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>6</v>
       </c>
@@ -3622,7 +3560,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>19</v>
       </c>
@@ -3633,7 +3571,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>19</v>
       </c>
@@ -3644,7 +3582,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>19</v>
       </c>
@@ -3655,7 +3593,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>19</v>
       </c>
@@ -3666,7 +3604,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>19</v>
       </c>
@@ -3677,7 +3615,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>19</v>
       </c>
@@ -3688,7 +3626,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>19</v>
       </c>
@@ -3699,7 +3637,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>19</v>
       </c>
@@ -3710,7 +3648,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>6</v>
       </c>
@@ -3721,7 +3659,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>6</v>
       </c>
@@ -3732,7 +3670,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>6</v>
       </c>
@@ -3743,7 +3681,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>6</v>
       </c>
@@ -3754,7 +3692,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>19</v>
       </c>
@@ -3765,7 +3703,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>19</v>
       </c>
@@ -3776,7 +3714,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>6</v>
       </c>
@@ -3793,7 +3731,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>6</v>
       </c>
@@ -3807,7 +3745,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>6</v>
       </c>
@@ -3818,7 +3756,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>6</v>
       </c>
@@ -3829,7 +3767,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>6</v>
       </c>
@@ -3840,7 +3778,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>6</v>
       </c>
@@ -3851,7 +3789,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>6</v>
       </c>
@@ -3862,7 +3800,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>19</v>
       </c>
@@ -3873,7 +3811,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>6</v>
       </c>
@@ -3884,7 +3822,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>6</v>
       </c>
@@ -3895,7 +3833,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>6</v>
       </c>
@@ -3906,7 +3844,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>6</v>
       </c>
@@ -3917,7 +3855,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>6</v>
       </c>
@@ -3928,7 +3866,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>6</v>
       </c>
@@ -3939,7 +3877,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>6</v>
       </c>
@@ -3950,7 +3888,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>6</v>
       </c>
@@ -3961,7 +3899,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>6</v>
       </c>
@@ -3972,7 +3910,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>6</v>
       </c>
@@ -3983,7 +3921,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>6</v>
       </c>
@@ -4000,7 +3938,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>6</v>
       </c>
@@ -4014,7 +3952,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>6</v>
       </c>
@@ -4028,7 +3966,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>6</v>
       </c>
@@ -4042,7 +3980,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>6</v>
       </c>
@@ -4056,7 +3994,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>6</v>
       </c>
@@ -4070,7 +4008,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>6</v>
       </c>
@@ -4081,7 +4019,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>6</v>
       </c>
@@ -4092,7 +4030,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>6</v>
       </c>
@@ -4103,7 +4041,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>6</v>
       </c>
@@ -4114,7 +4052,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>6</v>
       </c>
@@ -4128,7 +4066,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>6</v>
       </c>
@@ -4145,7 +4083,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>6</v>
       </c>
@@ -4159,7 +4097,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>6</v>
       </c>
@@ -4173,7 +4111,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>19</v>
       </c>
@@ -4187,7 +4125,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>6</v>
       </c>
@@ -4201,7 +4139,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>6</v>
       </c>
@@ -4215,7 +4153,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>6</v>
       </c>
@@ -4229,7 +4167,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>6</v>
       </c>
@@ -4243,7 +4181,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>6</v>
       </c>
@@ -4257,7 +4195,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>6</v>
       </c>
@@ -4271,7 +4209,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>6</v>
       </c>
@@ -4285,7 +4223,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>6</v>
       </c>
@@ -4299,7 +4237,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>6</v>
       </c>
@@ -4313,7 +4251,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>6</v>
       </c>
@@ -4327,7 +4265,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>6</v>
       </c>
@@ -4341,7 +4279,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>6</v>
       </c>
@@ -4355,7 +4293,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>6</v>
       </c>
@@ -4369,7 +4307,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>6</v>
       </c>
@@ -4383,7 +4321,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>6</v>
       </c>
@@ -4397,7 +4335,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>19</v>
       </c>
@@ -4411,7 +4349,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>6</v>
       </c>
@@ -4425,7 +4363,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>6</v>
       </c>
@@ -4439,7 +4377,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>6</v>
       </c>
@@ -4453,7 +4391,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>6</v>
       </c>
@@ -4467,7 +4405,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>19</v>
       </c>
@@ -4481,7 +4419,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>19</v>
       </c>
@@ -4495,7 +4433,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>19</v>
       </c>
@@ -4509,7 +4447,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>19</v>
       </c>
@@ -4523,7 +4461,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>6</v>
       </c>
@@ -4537,7 +4475,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>6</v>
       </c>
@@ -4551,7 +4489,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>6</v>
       </c>
@@ -4565,7 +4503,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>6</v>
       </c>
@@ -4579,7 +4517,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>6</v>
       </c>
@@ -4593,7 +4531,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>6</v>
       </c>
@@ -4607,7 +4545,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>6</v>
       </c>
@@ -4621,7 +4559,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>6</v>
       </c>
@@ -4635,7 +4573,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>6</v>
       </c>
@@ -4649,7 +4587,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>6</v>
       </c>
@@ -4660,7 +4598,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>6</v>
       </c>
@@ -4671,7 +4609,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>6</v>
       </c>
@@ -4682,7 +4620,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>6</v>
       </c>
@@ -4693,7 +4631,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>6</v>
       </c>
@@ -4704,7 +4642,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>6</v>
       </c>
@@ -4715,7 +4653,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>6</v>
       </c>
@@ -4726,7 +4664,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>19</v>
       </c>
@@ -4737,7 +4675,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>6</v>
       </c>
@@ -4751,7 +4689,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>6</v>
       </c>
@@ -4762,7 +4700,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>6</v>
       </c>
@@ -4773,7 +4711,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>6</v>
       </c>
@@ -4784,7 +4722,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>6</v>
       </c>
@@ -4795,7 +4733,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>6</v>
       </c>
@@ -4806,7 +4744,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>6</v>
       </c>
@@ -4817,7 +4755,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>6</v>
       </c>
@@ -4828,7 +4766,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>6</v>
       </c>
@@ -4839,7 +4777,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>15</v>
       </c>
@@ -4850,7 +4788,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>19</v>
       </c>
@@ -4861,7 +4799,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>19</v>
       </c>
@@ -4875,7 +4813,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>19</v>
       </c>
@@ -4886,7 +4824,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>6</v>
       </c>
@@ -4903,7 +4841,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>6</v>
       </c>
@@ -4920,7 +4858,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>6</v>
       </c>
@@ -4934,7 +4872,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>6</v>
       </c>
@@ -4948,7 +4886,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>6</v>
       </c>
@@ -4962,7 +4900,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>6</v>
       </c>
@@ -4976,7 +4914,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>6</v>
       </c>
@@ -4990,7 +4928,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>6</v>
       </c>
@@ -5001,7 +4939,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>6</v>
       </c>
@@ -5012,7 +4950,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>6</v>
       </c>
@@ -5023,7 +4961,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>6</v>
       </c>
@@ -5034,7 +4972,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>6</v>
       </c>
@@ -5045,7 +4983,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>6</v>
       </c>
@@ -5056,7 +4994,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>6</v>
       </c>
@@ -5067,7 +5005,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>6</v>
       </c>
@@ -5078,7 +5016,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>6</v>
       </c>
@@ -5089,7 +5027,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>6</v>
       </c>
@@ -5100,7 +5038,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>6</v>
       </c>
@@ -5111,7 +5049,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>6</v>
       </c>
@@ -5122,7 +5060,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>6</v>
       </c>
@@ -5133,7 +5071,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>6</v>
       </c>
@@ -5144,7 +5082,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>6</v>
       </c>
@@ -5155,7 +5093,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>6</v>
       </c>
@@ -5166,7 +5104,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>6</v>
       </c>
@@ -5177,7 +5115,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>6</v>
       </c>
@@ -5188,7 +5126,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>6</v>
       </c>
@@ -5199,7 +5137,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>6</v>
       </c>
@@ -5210,7 +5148,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>6</v>
       </c>
@@ -5221,7 +5159,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>6</v>
       </c>
@@ -5232,7 +5170,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>6</v>
       </c>
@@ -5243,7 +5181,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>6</v>
       </c>
@@ -5254,7 +5192,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>6</v>
       </c>
@@ -5265,7 +5203,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>6</v>
       </c>
@@ -5276,7 +5214,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>6</v>
       </c>
@@ -5287,7 +5225,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>6</v>
       </c>
@@ -5298,7 +5236,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>6</v>
       </c>
@@ -5309,7 +5247,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>6</v>
       </c>
@@ -5320,7 +5258,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>6</v>
       </c>
@@ -5331,7 +5269,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>6</v>
       </c>
@@ -5345,7 +5283,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>6</v>
       </c>
@@ -5359,7 +5297,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>6</v>
       </c>
@@ -5373,7 +5311,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>6</v>
       </c>
@@ -5387,7 +5325,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>6</v>
       </c>
@@ -5401,7 +5339,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>6</v>
       </c>
@@ -5415,7 +5353,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>6</v>
       </c>
@@ -5429,7 +5367,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>6</v>
       </c>
@@ -5443,7 +5381,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>6</v>
       </c>
@@ -5457,7 +5395,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>6</v>
       </c>
@@ -5471,7 +5409,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>6</v>
       </c>
@@ -5485,7 +5423,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>6</v>
       </c>
@@ -5499,7 +5437,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>15</v>
       </c>
@@ -5513,7 +5451,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>6</v>
       </c>
@@ -5524,7 +5462,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>6</v>
       </c>
@@ -5535,7 +5473,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>6</v>
       </c>
@@ -5549,7 +5487,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>6</v>
       </c>
@@ -5560,7 +5498,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>6</v>
       </c>
@@ -5571,7 +5509,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>6</v>
       </c>
@@ -5582,7 +5520,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>6</v>
       </c>
@@ -5593,7 +5531,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>6</v>
       </c>
@@ -5604,7 +5542,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>6</v>
       </c>
@@ -5615,7 +5553,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>6</v>
       </c>
@@ -5626,7 +5564,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>6</v>
       </c>
@@ -5637,7 +5575,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>6</v>
       </c>
@@ -5648,7 +5586,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>6</v>
       </c>
@@ -5659,7 +5597,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>6</v>
       </c>
@@ -5670,7 +5608,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>6</v>
       </c>
@@ -5681,7 +5619,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>6</v>
       </c>
@@ -5692,7 +5630,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>6</v>
       </c>
@@ -5703,7 +5641,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>6</v>
       </c>
@@ -5714,7 +5652,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>6</v>
       </c>
@@ -5725,7 +5663,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>6</v>
       </c>
@@ -5736,7 +5674,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>6</v>
       </c>
@@ -5747,7 +5685,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>6</v>
       </c>
@@ -5758,7 +5696,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>6</v>
       </c>
@@ -5769,7 +5707,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>15</v>
       </c>
@@ -5783,7 +5721,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>15</v>
       </c>
@@ -5794,7 +5732,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>15</v>
       </c>
@@ -5805,7 +5743,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>15</v>
       </c>
@@ -5816,7 +5754,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>15</v>
       </c>
@@ -5827,7 +5765,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>15</v>
       </c>
@@ -5838,7 +5776,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>15</v>
       </c>
@@ -5849,7 +5787,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>19</v>
       </c>
@@ -5863,7 +5801,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>19</v>
       </c>
@@ -5874,7 +5812,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>6</v>
       </c>
@@ -5885,7 +5823,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>6</v>
       </c>
@@ -5899,7 +5837,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>6</v>
       </c>
@@ -5910,7 +5848,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>6</v>
       </c>
@@ -5921,7 +5859,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>6</v>
       </c>
@@ -5935,7 +5873,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>6</v>
       </c>
@@ -5946,7 +5884,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>6</v>
       </c>
@@ -5957,7 +5895,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>6</v>
       </c>
@@ -5968,7 +5906,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>6</v>
       </c>
@@ -5979,7 +5917,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>6</v>
       </c>
@@ -5990,7 +5928,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>6</v>
       </c>
@@ -6001,7 +5939,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>6</v>
       </c>
@@ -6012,7 +5950,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>6</v>
       </c>
@@ -6023,7 +5961,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>6</v>
       </c>
@@ -6034,7 +5972,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>6</v>
       </c>
@@ -6045,7 +5983,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>6</v>
       </c>
@@ -6056,7 +5994,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>6</v>
       </c>
@@ -6067,7 +6005,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>6</v>
       </c>
@@ -6078,7 +6016,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>15</v>
       </c>
@@ -6089,7 +6027,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>6</v>
       </c>
@@ -6103,7 +6041,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>6</v>
       </c>
@@ -6117,7 +6055,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>6</v>
       </c>
@@ -6131,7 +6069,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>6</v>
       </c>
@@ -6145,7 +6083,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>6</v>
       </c>
@@ -6159,7 +6097,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>6</v>
       </c>
@@ -6173,7 +6111,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>6</v>
       </c>
@@ -6187,7 +6125,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>6</v>
       </c>
@@ -6201,7 +6139,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>6</v>
       </c>
@@ -6215,7 +6153,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>6</v>
       </c>
@@ -6229,7 +6167,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>6</v>
       </c>
@@ -6243,7 +6181,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>6</v>
       </c>
@@ -6257,7 +6195,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>6</v>
       </c>
@@ -6271,7 +6209,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>6</v>
       </c>
@@ -6285,7 +6223,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>6</v>
       </c>
@@ -6299,7 +6237,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>6</v>
       </c>
@@ -6313,7 +6251,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>6</v>
       </c>
@@ -6327,7 +6265,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>6</v>
       </c>
@@ -6341,7 +6279,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>6</v>
       </c>
@@ -6355,7 +6293,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>6</v>
       </c>
@@ -6369,7 +6307,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>15</v>
       </c>
@@ -6383,7 +6321,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>15</v>
       </c>
@@ -6397,7 +6335,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>6</v>
       </c>
@@ -6411,7 +6349,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>6</v>
       </c>
@@ -6425,7 +6363,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>15</v>
       </c>
@@ -6439,7 +6377,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>6</v>
       </c>
@@ -6453,7 +6391,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>15</v>
       </c>
@@ -6467,7 +6405,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>6</v>
       </c>
@@ -6481,7 +6419,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>15</v>
       </c>
@@ -6495,7 +6433,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>6</v>
       </c>
@@ -6509,7 +6447,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>15</v>
       </c>
@@ -6523,7 +6461,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>6</v>
       </c>
@@ -6537,7 +6475,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>15</v>
       </c>
@@ -6551,7 +6489,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>6</v>
       </c>
@@ -6565,7 +6503,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>6</v>
       </c>
@@ -6579,7 +6517,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>15</v>
       </c>
@@ -6593,7 +6531,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>6</v>
       </c>
@@ -6607,7 +6545,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>6</v>
       </c>
@@ -6621,7 +6559,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>6</v>
       </c>
@@ -6635,7 +6573,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>6</v>
       </c>
@@ -6649,7 +6587,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>15</v>
       </c>
@@ -6663,7 +6601,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>6</v>
       </c>
@@ -6677,7 +6615,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>6</v>
       </c>
@@ -6691,7 +6629,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>6</v>
       </c>
@@ -6705,7 +6643,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>6</v>
       </c>
@@ -6719,7 +6657,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>6</v>
       </c>
@@ -6733,7 +6671,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>19</v>
       </c>
@@ -6747,7 +6685,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>19</v>
       </c>
@@ -6761,7 +6699,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>19</v>
       </c>
@@ -6775,7 +6713,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>19</v>
       </c>
@@ -6789,7 +6727,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>19</v>
       </c>
@@ -6803,7 +6741,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>19</v>
       </c>
@@ -6817,7 +6755,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>19</v>
       </c>
@@ -6831,7 +6769,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>19</v>
       </c>
@@ -6845,7 +6783,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>19</v>
       </c>
@@ -6859,7 +6797,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>19</v>
       </c>
@@ -6873,7 +6811,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>19</v>
       </c>
@@ -6887,7 +6825,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>19</v>
       </c>
@@ -6901,7 +6839,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>19</v>
       </c>
@@ -6915,7 +6853,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>19</v>
       </c>
@@ -6929,7 +6867,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>19</v>
       </c>
@@ -6943,7 +6881,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>19</v>
       </c>
@@ -6957,7 +6895,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>19</v>
       </c>
@@ -6971,7 +6909,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>19</v>
       </c>
@@ -6985,7 +6923,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>19</v>
       </c>
@@ -6999,7 +6937,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>19</v>
       </c>
@@ -7013,7 +6951,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>19</v>
       </c>
@@ -7027,7 +6965,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>19</v>
       </c>
@@ -7041,7 +6979,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>19</v>
       </c>
@@ -7055,7 +6993,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>19</v>
       </c>
@@ -7069,7 +7007,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>19</v>
       </c>
@@ -7083,7 +7021,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>19</v>
       </c>
@@ -7097,7 +7035,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>19</v>
       </c>
@@ -7111,7 +7049,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>19</v>
       </c>
@@ -7125,7 +7063,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>19</v>
       </c>
@@ -7139,7 +7077,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>19</v>
       </c>
@@ -7153,7 +7091,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>19</v>
       </c>
@@ -7167,7 +7105,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>19</v>
       </c>
@@ -7181,7 +7119,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>19</v>
       </c>
@@ -7195,7 +7133,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>19</v>
       </c>
@@ -7209,7 +7147,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>19</v>
       </c>
@@ -7223,7 +7161,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>19</v>
       </c>
@@ -7237,7 +7175,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>19</v>
       </c>
@@ -7251,7 +7189,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>19</v>
       </c>
@@ -7265,7 +7203,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>19</v>
       </c>
@@ -7279,7 +7217,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>19</v>
       </c>
@@ -7293,7 +7231,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>19</v>
       </c>
@@ -7307,7 +7245,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>19</v>
       </c>
@@ -7321,7 +7259,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>19</v>
       </c>
@@ -7335,7 +7273,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>19</v>
       </c>
@@ -7349,7 +7287,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>19</v>
       </c>
@@ -7363,7 +7301,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>19</v>
       </c>
@@ -7377,7 +7315,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>19</v>
       </c>
@@ -7391,7 +7329,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>19</v>
       </c>
@@ -7405,7 +7343,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>19</v>
       </c>
@@ -7419,7 +7357,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>6</v>
       </c>
@@ -7433,7 +7371,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>19</v>
       </c>
@@ -7447,7 +7385,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>6</v>
       </c>
@@ -7461,7 +7399,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>19</v>
       </c>
@@ -7475,7 +7413,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>6</v>
       </c>
@@ -7489,7 +7427,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>19</v>
       </c>
@@ -7503,7 +7441,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>6</v>
       </c>
@@ -7517,7 +7455,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>19</v>
       </c>
@@ -7531,7 +7469,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>6</v>
       </c>
@@ -7545,7 +7483,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>19</v>
       </c>
@@ -7559,7 +7497,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>6</v>
       </c>
@@ -7573,7 +7511,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>19</v>
       </c>
@@ -7587,7 +7525,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>6</v>
       </c>
@@ -7601,7 +7539,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>19</v>
       </c>
@@ -7615,7 +7553,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>6</v>
       </c>
@@ -7629,7 +7567,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>19</v>
       </c>
@@ -7643,7 +7581,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>6</v>
       </c>
@@ -7657,7 +7595,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>19</v>
       </c>
@@ -7671,7 +7609,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>19</v>
       </c>
@@ -7685,7 +7623,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>19</v>
       </c>
@@ -7699,7 +7637,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>19</v>
       </c>
@@ -7713,7 +7651,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>19</v>
       </c>
@@ -7727,7 +7665,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>6</v>
       </c>
@@ -7741,7 +7679,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>6</v>
       </c>
@@ -7755,7 +7693,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>28</v>
       </c>
@@ -7769,7 +7707,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>28</v>
       </c>
@@ -7783,7 +7721,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>28</v>
       </c>
@@ -7797,7 +7735,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>19</v>
       </c>
@@ -7811,7 +7749,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>19</v>
       </c>
@@ -7825,7 +7763,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>19</v>
       </c>
@@ -7839,7 +7777,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>19</v>
       </c>
@@ -7853,7 +7791,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>19</v>
       </c>
@@ -7867,7 +7805,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>19</v>
       </c>
@@ -7881,7 +7819,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>19</v>
       </c>
@@ -7895,7 +7833,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>19</v>
       </c>
@@ -7909,7 +7847,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>28</v>
       </c>
@@ -7923,7 +7861,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>6</v>
       </c>
@@ -7937,7 +7875,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>6</v>
       </c>
@@ -7951,7 +7889,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>28</v>
       </c>
@@ -7965,7 +7903,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>28</v>
       </c>
@@ -7979,7 +7917,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>6</v>
       </c>
@@ -7993,7 +7931,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>28</v>
       </c>
@@ -8007,7 +7945,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>28</v>
       </c>
@@ -8021,7 +7959,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>6</v>
       </c>
@@ -8035,7 +7973,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>6</v>
       </c>
@@ -8049,7 +7987,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>6</v>
       </c>
@@ -8063,7 +8001,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>6</v>
       </c>
@@ -8077,7 +8015,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>6</v>
       </c>
@@ -8091,7 +8029,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>6</v>
       </c>
@@ -8105,7 +8043,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>6</v>
       </c>
@@ -8119,7 +8057,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>6</v>
       </c>
@@ -8133,7 +8071,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>6</v>
       </c>
@@ -8147,7 +8085,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>6</v>
       </c>
@@ -8161,7 +8099,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>6</v>
       </c>
@@ -8175,7 +8113,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>6</v>
       </c>
@@ -8189,7 +8127,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>6</v>
       </c>
@@ -8203,7 +8141,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>15</v>
       </c>
@@ -8217,7 +8155,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>6</v>
       </c>
@@ -8231,7 +8169,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>6</v>
       </c>
@@ -8245,7 +8183,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>6</v>
       </c>
@@ -8259,7 +8197,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>6</v>
       </c>
@@ -8273,7 +8211,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>6</v>
       </c>
@@ -8287,7 +8225,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>6</v>
       </c>
@@ -8301,7 +8239,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>6</v>
       </c>
@@ -8315,7 +8253,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>6</v>
       </c>
@@ -8329,7 +8267,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>6</v>
       </c>
@@ -8343,7 +8281,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>6</v>
       </c>
@@ -8357,7 +8295,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>6</v>
       </c>
@@ -8371,7 +8309,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>6</v>
       </c>
@@ -8385,7 +8323,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>6</v>
       </c>
@@ -8399,7 +8337,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>6</v>
       </c>
@@ -8413,7 +8351,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>6</v>
       </c>
@@ -8427,7 +8365,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>28</v>
       </c>
@@ -8441,7 +8379,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>28</v>
       </c>
@@ -8455,7 +8393,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>28</v>
       </c>
@@ -8466,7 +8404,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>6</v>
       </c>
@@ -8480,7 +8418,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>6</v>
       </c>
@@ -8494,7 +8432,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>6</v>
       </c>
@@ -8508,7 +8446,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>6</v>
       </c>
@@ -8522,7 +8460,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>6</v>
       </c>
@@ -8536,7 +8474,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>6</v>
       </c>
@@ -8550,7 +8488,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>6</v>
       </c>
@@ -8564,7 +8502,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>6</v>
       </c>
@@ -8578,7 +8516,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>6</v>
       </c>
@@ -8592,7 +8530,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>6</v>
       </c>
@@ -8606,7 +8544,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>6</v>
       </c>
@@ -8620,7 +8558,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>6</v>
       </c>
@@ -8634,7 +8572,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>6</v>
       </c>
@@ -8648,7 +8586,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>6</v>
       </c>
@@ -8662,7 +8600,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>6</v>
       </c>
@@ -8676,7 +8614,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>6</v>
       </c>
@@ -8690,7 +8628,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>6</v>
       </c>
@@ -8704,7 +8642,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>6</v>
       </c>
@@ -8718,7 +8656,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>6</v>
       </c>
@@ -8732,7 +8670,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>6</v>
       </c>
@@ -8746,7 +8684,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>6</v>
       </c>
@@ -8760,7 +8698,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>6</v>
       </c>
@@ -8774,7 +8712,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>6</v>
       </c>
@@ -8788,7 +8726,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>6</v>
       </c>
@@ -8802,7 +8740,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>6</v>
       </c>
@@ -8816,7 +8754,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>6</v>
       </c>
@@ -8830,7 +8768,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>6</v>
       </c>
@@ -8844,7 +8782,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>6</v>
       </c>
@@ -8858,7 +8796,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>6</v>
       </c>
@@ -8872,7 +8810,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>6</v>
       </c>
@@ -8886,7 +8824,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>6</v>
       </c>
@@ -8900,7 +8838,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>6</v>
       </c>
@@ -8914,7 +8852,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>6</v>
       </c>
@@ -8928,7 +8866,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>6</v>
       </c>
@@ -8942,7 +8880,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>6</v>
       </c>
@@ -8956,7 +8894,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>6</v>
       </c>
@@ -8970,7 +8908,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>6</v>
       </c>
@@ -8984,7 +8922,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>6</v>
       </c>
@@ -8998,7 +8936,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>6</v>
       </c>
@@ -9012,7 +8950,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>6</v>
       </c>
@@ -9026,7 +8964,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>28</v>
       </c>
@@ -9040,7 +8978,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>28</v>
       </c>
@@ -9054,7 +8992,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>28</v>
       </c>
@@ -9068,7 +9006,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>6</v>
       </c>
@@ -9082,7 +9020,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="549" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>6</v>
       </c>
@@ -9096,7 +9034,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>6</v>
       </c>
@@ -9110,7 +9048,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="551" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="551" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>6</v>
       </c>
@@ -9124,7 +9062,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>6</v>
       </c>
@@ -9138,7 +9076,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="553" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="553" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>6</v>
       </c>
@@ -9152,7 +9090,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="554" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>6</v>
       </c>
@@ -9166,7 +9104,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="555" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="555" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>6</v>
       </c>
@@ -9180,7 +9118,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="556" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="556" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>6</v>
       </c>
@@ -9194,7 +9132,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="557" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>6</v>
       </c>
@@ -9208,7 +9146,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="558" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="558" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>6</v>
       </c>
@@ -9222,7 +9160,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="559" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>19</v>
       </c>
@@ -9236,7 +9174,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="560" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="560" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>6</v>
       </c>
@@ -9250,7 +9188,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>6</v>
       </c>
@@ -9264,7 +9202,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>6</v>
       </c>
@@ -9278,7 +9216,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>6</v>
       </c>
@@ -9292,7 +9230,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>6</v>
       </c>
@@ -9306,7 +9244,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="565" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="565" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>6</v>
       </c>
@@ -9320,7 +9258,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="566" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="566" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>6</v>
       </c>
@@ -9334,7 +9272,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>6</v>
       </c>
@@ -9348,7 +9286,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="568" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>6</v>
       </c>
@@ -9362,7 +9300,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="569" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>6</v>
       </c>
@@ -9376,7 +9314,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="570" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="570" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>6</v>
       </c>
@@ -9390,7 +9328,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="571" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="571" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>6</v>
       </c>
@@ -9404,7 +9342,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="572" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="572" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>6</v>
       </c>
@@ -9418,7 +9356,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="573" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="573" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>6</v>
       </c>
@@ -9432,7 +9370,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="574" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>6</v>
       </c>
@@ -9446,7 +9384,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="575" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="575" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>6</v>
       </c>
@@ -9460,7 +9398,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="576" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="576" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>6</v>
       </c>
@@ -9474,7 +9412,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="577" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="577" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>6</v>
       </c>
@@ -9488,7 +9426,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="578" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="578" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>6</v>
       </c>
@@ -9502,7 +9440,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="579" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="579" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>6</v>
       </c>
@@ -9516,7 +9454,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="580" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="580" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>6</v>
       </c>
@@ -9530,7 +9468,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="581" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="581" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>6</v>
       </c>
@@ -9544,7 +9482,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="582" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="582" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>6</v>
       </c>
@@ -9558,7 +9496,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="583" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="583" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>6</v>
       </c>
@@ -9572,7 +9510,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="584" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="584" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>28</v>
       </c>
@@ -9586,7 +9524,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="585" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="585" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>15</v>
       </c>
@@ -9600,7 +9538,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="586" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="586" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>6</v>
       </c>
@@ -9614,7 +9552,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="587" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="587" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>6</v>
       </c>
@@ -9628,7 +9566,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="588" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="588" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>6</v>
       </c>
@@ -9642,7 +9580,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="589" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="589" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>6</v>
       </c>
@@ -9656,7 +9594,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="590" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="590" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>6</v>
       </c>
@@ -9670,7 +9608,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="591" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="591" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>6</v>
       </c>
@@ -9684,7 +9622,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="592" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="592" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>6</v>
       </c>
@@ -9698,7 +9636,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="593" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="593" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>6</v>
       </c>
@@ -9712,7 +9650,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="594" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="594" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>6</v>
       </c>
@@ -9726,7 +9664,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="595" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="595" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>6</v>
       </c>
@@ -9740,7 +9678,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="596" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="596" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>6</v>
       </c>
@@ -9754,7 +9692,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="597" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="597" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>6</v>
       </c>
@@ -9768,7 +9706,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="598" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="598" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>6</v>
       </c>
@@ -9782,7 +9720,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="599" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="599" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>15</v>
       </c>
@@ -9796,7 +9734,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="600" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="600" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>15</v>
       </c>
@@ -9813,7 +9751,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="601" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="601" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>6</v>
       </c>
@@ -9827,7 +9765,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="602" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="602" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>6</v>
       </c>
@@ -9841,7 +9779,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="603" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="603" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>6</v>
       </c>
@@ -9855,7 +9793,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="604" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="604" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>6</v>
       </c>
@@ -9869,7 +9807,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="605" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="605" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>6</v>
       </c>
@@ -9883,7 +9821,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="606" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="606" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>6</v>
       </c>
@@ -9897,7 +9835,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="607" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="607" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>6</v>
       </c>
@@ -9911,7 +9849,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="608" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="608" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>6</v>
       </c>
@@ -9925,7 +9863,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="609" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="609" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>6</v>
       </c>
@@ -9939,7 +9877,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="610" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="610" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>6</v>
       </c>
@@ -9953,7 +9891,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="611" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="611" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>6</v>
       </c>
@@ -9967,7 +9905,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="612" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="612" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>6</v>
       </c>
@@ -9981,7 +9919,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="613" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="613" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>6</v>
       </c>
@@ -9995,7 +9933,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="614" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="614" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>6</v>
       </c>
@@ -10009,7 +9947,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="615" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="615" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>6</v>
       </c>
@@ -10023,7 +9961,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="616" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="616" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>6</v>
       </c>
@@ -10037,7 +9975,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="617" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="617" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>6</v>
       </c>
@@ -10051,7 +9989,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="618" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="618" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>6</v>
       </c>
@@ -10065,7 +10003,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="619" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="619" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>6</v>
       </c>
@@ -10079,7 +10017,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="620" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="620" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>6</v>
       </c>
@@ -10093,7 +10031,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="621" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="621" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>6</v>
       </c>
@@ -10107,7 +10045,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="622" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="622" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>6</v>
       </c>
@@ -10121,7 +10059,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="623" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="623" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>6</v>
       </c>
@@ -10135,7 +10073,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="624" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="624" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>6</v>
       </c>
@@ -10149,7 +10087,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="625" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="625" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>6</v>
       </c>
@@ -10163,7 +10101,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="626" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="626" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>15</v>
       </c>
@@ -10177,7 +10115,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="627" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="627" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>6</v>
       </c>
@@ -10191,7 +10129,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="628" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="628" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>6</v>
       </c>
@@ -10205,7 +10143,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="629" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="629" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>15</v>
       </c>
@@ -10219,7 +10157,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="630" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="630" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>6</v>
       </c>
@@ -10233,7 +10171,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="631" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="631" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>15</v>
       </c>
@@ -10247,7 +10185,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="632" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="632" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>15</v>
       </c>
@@ -10258,7 +10196,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="633" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="633" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>15</v>
       </c>
@@ -10269,7 +10207,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="634" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="634" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>6</v>
       </c>
@@ -10283,7 +10221,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="635" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="635" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>6</v>
       </c>
@@ -10294,7 +10232,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="636" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="636" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>6</v>
       </c>
@@ -10308,7 +10246,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="637" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="637" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>28</v>
       </c>
@@ -10322,7 +10260,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="638" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="638" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>6</v>
       </c>
@@ -10336,7 +10274,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="639" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="639" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>28</v>
       </c>
@@ -10350,7 +10288,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="640" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="640" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>6</v>
       </c>
@@ -10364,7 +10302,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="641" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="641" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>6</v>
       </c>
@@ -10378,7 +10316,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="642" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="642" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>6</v>
       </c>
@@ -10392,7 +10330,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="643" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="643" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>6</v>
       </c>
@@ -10406,7 +10344,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="644" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="644" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>6</v>
       </c>
@@ -10420,7 +10358,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="645" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="645" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>6</v>
       </c>
@@ -10434,7 +10372,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="646" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="646" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>6</v>
       </c>
@@ -10448,7 +10386,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="647" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="647" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>6</v>
       </c>
@@ -10462,7 +10400,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="648" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="648" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>6</v>
       </c>
@@ -10476,7 +10414,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="649" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="649" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>6</v>
       </c>
@@ -10490,7 +10428,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="650" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="650" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>6</v>
       </c>
@@ -10504,7 +10442,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="651" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="651" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>6</v>
       </c>
@@ -10518,7 +10456,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="652" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="652" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>6</v>
       </c>
@@ -10532,7 +10470,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="653" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="653" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>6</v>
       </c>
@@ -10546,7 +10484,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="654" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="654" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>6</v>
       </c>
@@ -10560,7 +10498,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="655" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="655" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>6</v>
       </c>
@@ -10574,7 +10512,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="656" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="656" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>28</v>
       </c>
@@ -10588,7 +10526,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="657" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="657" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>6</v>
       </c>
@@ -10602,7 +10540,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="658" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="658" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>6</v>
       </c>
@@ -10616,7 +10554,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="659" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="659" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>15</v>
       </c>
@@ -10630,7 +10568,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="660" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="660" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>6</v>
       </c>
@@ -10644,7 +10582,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="661" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="661" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>15</v>
       </c>
@@ -10658,7 +10596,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="662" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="662" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>6</v>
       </c>
@@ -10672,7 +10610,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="663" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="663" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>15</v>
       </c>
@@ -10686,7 +10624,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="664" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="664" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>6</v>
       </c>
@@ -10700,7 +10638,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="665" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="665" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>15</v>
       </c>
@@ -10714,7 +10652,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="666" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="666" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>6</v>
       </c>
@@ -10728,7 +10666,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="667" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="667" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>15</v>
       </c>
@@ -10742,7 +10680,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="668" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="668" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>6</v>
       </c>
@@ -10756,7 +10694,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="669" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="669" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>15</v>
       </c>
@@ -10770,7 +10708,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="670" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="670" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>6</v>
       </c>
@@ -10784,7 +10722,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="671" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="671" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>15</v>
       </c>
@@ -10798,7 +10736,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="672" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="672" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>6</v>
       </c>
@@ -10812,7 +10750,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="673" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="673" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>15</v>
       </c>
@@ -10826,7 +10764,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="674" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="674" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>6</v>
       </c>
@@ -10840,7 +10778,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="675" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="675" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>15</v>
       </c>
@@ -10854,7 +10792,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="676" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="676" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>6</v>
       </c>
@@ -10868,7 +10806,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="677" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="677" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>28</v>
       </c>
@@ -10882,7 +10820,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="678" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="678" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>6</v>
       </c>
@@ -10896,7 +10834,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="679" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="679" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>6</v>
       </c>
@@ -10910,7 +10848,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="680" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="680" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>6</v>
       </c>
@@ -10924,7 +10862,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="681" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="681" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>6</v>
       </c>
@@ -10938,7 +10876,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="682" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="682" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>6</v>
       </c>
@@ -10952,7 +10890,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="683" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="683" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>6</v>
       </c>
@@ -10966,7 +10904,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="684" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="684" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>6</v>
       </c>
@@ -10980,7 +10918,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="685" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="685" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>6</v>
       </c>
@@ -10994,7 +10932,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="686" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="686" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>6</v>
       </c>
@@ -11008,7 +10946,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="687" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="687" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>6</v>
       </c>
@@ -11022,7 +10960,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="688" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="688" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>6</v>
       </c>
@@ -11036,7 +10974,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="689" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="689" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>6</v>
       </c>
@@ -11050,7 +10988,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="690" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="690" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>28</v>
       </c>
@@ -11064,7 +11002,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="691" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="691" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>28</v>
       </c>
@@ -11078,7 +11016,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="692" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="692" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>6</v>
       </c>
@@ -11092,7 +11030,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="693" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="693" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>6</v>
       </c>
@@ -11106,7 +11044,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="694" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="694" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>6</v>
       </c>
@@ -11120,7 +11058,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="695" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="695" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>6</v>
       </c>
@@ -11134,7 +11072,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="696" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="696" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>6</v>
       </c>
@@ -11148,7 +11086,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="697" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="697" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>6</v>
       </c>
@@ -11162,7 +11100,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="698" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="698" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>6</v>
       </c>
@@ -11176,7 +11114,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="699" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="699" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>6</v>
       </c>
@@ -11190,7 +11128,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="700" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="700" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>6</v>
       </c>
@@ -11204,7 +11142,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="701" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="701" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>28</v>
       </c>
@@ -11218,7 +11156,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="702" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="702" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>28</v>
       </c>
@@ -11232,7 +11170,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="703" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="703" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>28</v>
       </c>
@@ -11246,7 +11184,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="704" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="704" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>6</v>
       </c>
@@ -11260,7 +11198,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="705" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="705" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>6</v>
       </c>
@@ -11274,7 +11212,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="706" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="706" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>6</v>
       </c>
@@ -11286,6 +11224,62 @@
       </c>
       <c r="D706" t="s">
         <v>537</v>
+      </c>
+    </row>
+    <row r="707" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A707" t="s">
+        <v>6</v>
+      </c>
+      <c r="B707">
+        <v>2603</v>
+      </c>
+      <c r="C707" t="s">
+        <v>538</v>
+      </c>
+      <c r="D707" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="708" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A708" t="s">
+        <v>6</v>
+      </c>
+      <c r="B708">
+        <v>2606</v>
+      </c>
+      <c r="C708" t="s">
+        <v>538</v>
+      </c>
+      <c r="D708" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="709" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A709" t="s">
+        <v>6</v>
+      </c>
+      <c r="B709">
+        <v>23415</v>
+      </c>
+      <c r="C709" t="s">
+        <v>539</v>
+      </c>
+      <c r="D709" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="710" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A710" t="s">
+        <v>6</v>
+      </c>
+      <c r="B710">
+        <v>23416</v>
+      </c>
+      <c r="C710" t="s">
+        <v>539</v>
+      </c>
+      <c r="D710" t="s">
+        <v>539</v>
       </c>
     </row>
   </sheetData>

--- a/Files/Controls.xlsx
+++ b/Files/Controls.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\NVDA\VismaAdministration\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D8B9246-DD08-4391-A200-437D5C9D8CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA87390-790B-4A54-9E61-0C4ED34C4F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1425" yWindow="1425" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1919" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1985" uniqueCount="545">
   <si>
     <t>WindowClassName</t>
   </si>
@@ -1653,6 +1653,21 @@
   </si>
   <si>
     <t>Lösenord</t>
+  </si>
+  <si>
+    <t>Lönummer</t>
+  </si>
+  <si>
+    <t>Antal</t>
+  </si>
+  <si>
+    <t>Pris styck</t>
+  </si>
+  <si>
+    <t>Frakt styck</t>
+  </si>
+  <si>
+    <t>Kommentar</t>
   </si>
 </sst>
 </file>
@@ -1971,7 +1986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E710"/>
+  <dimension ref="A1:E732"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
@@ -11282,6 +11297,314 @@
         <v>539</v>
       </c>
     </row>
+    <row r="711" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A711" t="s">
+        <v>6</v>
+      </c>
+      <c r="B711">
+        <v>22825</v>
+      </c>
+      <c r="C711" t="s">
+        <v>254</v>
+      </c>
+      <c r="D711" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="712" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A712" t="s">
+        <v>6</v>
+      </c>
+      <c r="B712">
+        <v>22818</v>
+      </c>
+      <c r="C712" t="s">
+        <v>254</v>
+      </c>
+      <c r="D712" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="713" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A713" t="s">
+        <v>6</v>
+      </c>
+      <c r="B713">
+        <v>22828</v>
+      </c>
+      <c r="C713" t="s">
+        <v>254</v>
+      </c>
+      <c r="D713" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="714" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A714" t="s">
+        <v>6</v>
+      </c>
+      <c r="B714">
+        <v>22613</v>
+      </c>
+      <c r="C714" t="s">
+        <v>254</v>
+      </c>
+      <c r="D714" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="715" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A715" t="s">
+        <v>6</v>
+      </c>
+      <c r="B715">
+        <v>22619</v>
+      </c>
+      <c r="C715" t="s">
+        <v>254</v>
+      </c>
+      <c r="D715" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="716" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A716" t="s">
+        <v>6</v>
+      </c>
+      <c r="B716">
+        <v>22831</v>
+      </c>
+      <c r="C716" t="s">
+        <v>254</v>
+      </c>
+      <c r="D716" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="717" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A717" t="s">
+        <v>6</v>
+      </c>
+      <c r="B717">
+        <v>22834</v>
+      </c>
+      <c r="C717" t="s">
+        <v>254</v>
+      </c>
+      <c r="D717" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="718" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A718" t="s">
+        <v>6</v>
+      </c>
+      <c r="B718">
+        <v>22835</v>
+      </c>
+      <c r="C718" t="s">
+        <v>254</v>
+      </c>
+      <c r="D718" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="719" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A719" t="s">
+        <v>6</v>
+      </c>
+      <c r="B719">
+        <v>22846</v>
+      </c>
+      <c r="C719" t="s">
+        <v>254</v>
+      </c>
+      <c r="D719" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="720" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A720" t="s">
+        <v>6</v>
+      </c>
+      <c r="B720">
+        <v>22843</v>
+      </c>
+      <c r="C720" t="s">
+        <v>254</v>
+      </c>
+      <c r="D720" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="721" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A721" t="s">
+        <v>6</v>
+      </c>
+      <c r="B721">
+        <v>22844</v>
+      </c>
+      <c r="C721" t="s">
+        <v>254</v>
+      </c>
+      <c r="D721" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="722" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A722" t="s">
+        <v>6</v>
+      </c>
+      <c r="B722">
+        <v>22845</v>
+      </c>
+      <c r="C722" t="s">
+        <v>254</v>
+      </c>
+      <c r="D722" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="723" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A723" t="s">
+        <v>6</v>
+      </c>
+      <c r="B723">
+        <v>22825</v>
+      </c>
+      <c r="C723" t="s">
+        <v>256</v>
+      </c>
+      <c r="D723" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="724" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A724" t="s">
+        <v>6</v>
+      </c>
+      <c r="B724">
+        <v>22818</v>
+      </c>
+      <c r="C724" t="s">
+        <v>256</v>
+      </c>
+      <c r="D724" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="725" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A725" t="s">
+        <v>6</v>
+      </c>
+      <c r="B725">
+        <v>22828</v>
+      </c>
+      <c r="C725" t="s">
+        <v>256</v>
+      </c>
+      <c r="D725" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="726" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A726" t="s">
+        <v>6</v>
+      </c>
+      <c r="B726">
+        <v>22613</v>
+      </c>
+      <c r="C726" t="s">
+        <v>256</v>
+      </c>
+      <c r="D726" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="727" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A727" t="s">
+        <v>6</v>
+      </c>
+      <c r="B727">
+        <v>22619</v>
+      </c>
+      <c r="C727" t="s">
+        <v>256</v>
+      </c>
+      <c r="D727" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="728" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A728" t="s">
+        <v>6</v>
+      </c>
+      <c r="B728">
+        <v>22831</v>
+      </c>
+      <c r="C728" t="s">
+        <v>256</v>
+      </c>
+      <c r="D728" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="729" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A729" t="s">
+        <v>6</v>
+      </c>
+      <c r="B729">
+        <v>22846</v>
+      </c>
+      <c r="C729" t="s">
+        <v>256</v>
+      </c>
+      <c r="D729" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="730" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A730" t="s">
+        <v>6</v>
+      </c>
+      <c r="B730">
+        <v>22843</v>
+      </c>
+      <c r="C730" t="s">
+        <v>256</v>
+      </c>
+      <c r="D730" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="731" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A731" t="s">
+        <v>6</v>
+      </c>
+      <c r="B731">
+        <v>22844</v>
+      </c>
+      <c r="C731" t="s">
+        <v>256</v>
+      </c>
+      <c r="D731" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="732" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A732" t="s">
+        <v>6</v>
+      </c>
+      <c r="B732">
+        <v>22845</v>
+      </c>
+      <c r="C732" t="s">
+        <v>256</v>
+      </c>
+      <c r="D732" t="s">
+        <v>63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Files/Controls.xlsx
+++ b/Files/Controls.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\NVDA\VismaAdministration\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA87390-790B-4A54-9E61-0C4ED34C4F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C259FE-284F-4572-92A6-76F4C897C2DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1425" yWindow="1425" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1985" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1997" uniqueCount="546">
   <si>
     <t>WindowClassName</t>
   </si>
@@ -1668,6 +1668,9 @@
   </si>
   <si>
     <t>Kommentar</t>
+  </si>
+  <si>
+    <t>Anmärkning 3</t>
   </si>
 </sst>
 </file>
@@ -1986,7 +1989,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E732"/>
+  <dimension ref="A1:E736"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
@@ -11605,6 +11608,62 @@
         <v>63</v>
       </c>
     </row>
+    <row r="733" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A733" t="s">
+        <v>6</v>
+      </c>
+      <c r="B733">
+        <v>24583</v>
+      </c>
+      <c r="C733" t="s">
+        <v>250</v>
+      </c>
+      <c r="D733" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="734" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A734" t="s">
+        <v>6</v>
+      </c>
+      <c r="B734">
+        <v>23261</v>
+      </c>
+      <c r="C734" t="s">
+        <v>250</v>
+      </c>
+      <c r="D734" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="735" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A735" t="s">
+        <v>6</v>
+      </c>
+      <c r="B735">
+        <v>23262</v>
+      </c>
+      <c r="C735" t="s">
+        <v>250</v>
+      </c>
+      <c r="D735" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="736" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A736" t="s">
+        <v>6</v>
+      </c>
+      <c r="B736">
+        <v>23263</v>
+      </c>
+      <c r="C736" t="s">
+        <v>250</v>
+      </c>
+      <c r="D736" t="s">
+        <v>545</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Files/Controls.xlsx
+++ b/Files/Controls.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\NVDA\VismaAdministration\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C259FE-284F-4572-92A6-76F4C897C2DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77FBB7D1-1CAD-4A33-8F3E-DA955BEEA3D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1997" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2030" uniqueCount="546">
   <si>
     <t>WindowClassName</t>
   </si>
@@ -2456,6 +2456,9 @@
       <c r="B34">
         <v>22613</v>
       </c>
+      <c r="C34" t="s">
+        <v>243</v>
+      </c>
       <c r="D34" t="s">
         <v>8</v>
       </c>
@@ -2467,6 +2470,9 @@
       <c r="B35">
         <v>22614</v>
       </c>
+      <c r="C35" t="s">
+        <v>243</v>
+      </c>
       <c r="D35" t="s">
         <v>9</v>
       </c>
@@ -2478,6 +2484,9 @@
       <c r="B36">
         <v>22615</v>
       </c>
+      <c r="C36" t="s">
+        <v>243</v>
+      </c>
       <c r="D36" t="s">
         <v>10</v>
       </c>
@@ -2489,6 +2498,9 @@
       <c r="B37">
         <v>22616</v>
       </c>
+      <c r="C37" t="s">
+        <v>243</v>
+      </c>
       <c r="D37" t="s">
         <v>11</v>
       </c>
@@ -2500,6 +2512,9 @@
       <c r="B38">
         <v>22619</v>
       </c>
+      <c r="C38" t="s">
+        <v>243</v>
+      </c>
       <c r="D38" t="s">
         <v>12</v>
       </c>
@@ -2511,6 +2526,9 @@
       <c r="B39">
         <v>22617</v>
       </c>
+      <c r="C39" t="s">
+        <v>243</v>
+      </c>
       <c r="D39" t="s">
         <v>13</v>
       </c>
@@ -2521,6 +2539,9 @@
       </c>
       <c r="B40">
         <v>22709</v>
+      </c>
+      <c r="C40" t="s">
+        <v>243</v>
       </c>
       <c r="D40" t="s">
         <v>14</v>
@@ -2533,6 +2554,9 @@
       <c r="B41">
         <v>21657</v>
       </c>
+      <c r="C41" t="s">
+        <v>243</v>
+      </c>
       <c r="D41" t="s">
         <v>16</v>
       </c>
@@ -2544,6 +2568,9 @@
       <c r="B42">
         <v>22620</v>
       </c>
+      <c r="C42" t="s">
+        <v>243</v>
+      </c>
       <c r="D42" t="s">
         <v>17</v>
       </c>
@@ -2554,6 +2581,9 @@
       </c>
       <c r="B43">
         <v>22643</v>
+      </c>
+      <c r="C43" t="s">
+        <v>243</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
@@ -2566,6 +2596,9 @@
       <c r="B44">
         <v>22641</v>
       </c>
+      <c r="C44" t="s">
+        <v>243</v>
+      </c>
       <c r="D44" t="s">
         <v>20</v>
       </c>
@@ -2577,6 +2610,9 @@
       <c r="B45">
         <v>22618</v>
       </c>
+      <c r="C45" t="s">
+        <v>243</v>
+      </c>
       <c r="D45" t="s">
         <v>21</v>
       </c>
@@ -2588,6 +2624,9 @@
       <c r="B46">
         <v>22652</v>
       </c>
+      <c r="C46" t="s">
+        <v>243</v>
+      </c>
       <c r="D46" t="s">
         <v>22</v>
       </c>
@@ -2599,6 +2638,9 @@
       <c r="B47">
         <v>25050</v>
       </c>
+      <c r="C47" t="s">
+        <v>243</v>
+      </c>
       <c r="D47" t="s">
         <v>23</v>
       </c>
@@ -2610,6 +2652,9 @@
       <c r="B48">
         <v>23606</v>
       </c>
+      <c r="C48" t="s">
+        <v>243</v>
+      </c>
       <c r="D48" t="s">
         <v>24</v>
       </c>
@@ -2621,6 +2666,9 @@
       <c r="B49">
         <v>22708</v>
       </c>
+      <c r="C49" t="s">
+        <v>243</v>
+      </c>
       <c r="D49" t="s">
         <v>25</v>
       </c>
@@ -2632,6 +2680,9 @@
       <c r="B50">
         <v>22644</v>
       </c>
+      <c r="C50" t="s">
+        <v>243</v>
+      </c>
       <c r="D50" t="s">
         <v>26</v>
       </c>
@@ -2643,6 +2694,9 @@
       <c r="B51">
         <v>22645</v>
       </c>
+      <c r="C51" t="s">
+        <v>243</v>
+      </c>
       <c r="D51" t="s">
         <v>27</v>
       </c>
@@ -2654,6 +2708,9 @@
       <c r="B52">
         <v>20593</v>
       </c>
+      <c r="C52" t="s">
+        <v>243</v>
+      </c>
       <c r="D52" t="s">
         <v>296</v>
       </c>
@@ -2665,6 +2722,9 @@
       <c r="B53">
         <v>24279</v>
       </c>
+      <c r="C53" t="s">
+        <v>243</v>
+      </c>
       <c r="D53" t="s">
         <v>33</v>
       </c>
@@ -2679,6 +2739,9 @@
       <c r="B54">
         <v>22642</v>
       </c>
+      <c r="C54" t="s">
+        <v>243</v>
+      </c>
       <c r="D54" t="s">
         <v>34</v>
       </c>
@@ -2690,6 +2753,9 @@
       <c r="B55">
         <v>22628</v>
       </c>
+      <c r="C55" t="s">
+        <v>243</v>
+      </c>
       <c r="D55" t="s">
         <v>35</v>
       </c>
@@ -2701,6 +2767,9 @@
       <c r="B56">
         <v>22629</v>
       </c>
+      <c r="C56" t="s">
+        <v>243</v>
+      </c>
       <c r="D56" t="s">
         <v>36</v>
       </c>
@@ -2711,6 +2780,9 @@
       </c>
       <c r="B57">
         <v>22630</v>
+      </c>
+      <c r="C57" t="s">
+        <v>243</v>
       </c>
       <c r="D57" t="s">
         <v>37</v>
@@ -2723,6 +2795,9 @@
       <c r="B58">
         <v>22657</v>
       </c>
+      <c r="C58" t="s">
+        <v>243</v>
+      </c>
       <c r="D58" t="s">
         <v>38</v>
       </c>
@@ -2734,6 +2809,9 @@
       <c r="B59">
         <v>22627</v>
       </c>
+      <c r="C59" t="s">
+        <v>243</v>
+      </c>
       <c r="D59" t="s">
         <v>40</v>
       </c>
@@ -2748,6 +2826,9 @@
       <c r="B60">
         <v>22631</v>
       </c>
+      <c r="C60" t="s">
+        <v>243</v>
+      </c>
       <c r="D60" t="s">
         <v>41</v>
       </c>
@@ -2759,6 +2840,9 @@
       <c r="B61">
         <v>22653</v>
       </c>
+      <c r="C61" t="s">
+        <v>243</v>
+      </c>
       <c r="D61" t="s">
         <v>42</v>
       </c>
@@ -2770,6 +2854,9 @@
       <c r="B62">
         <v>22654</v>
       </c>
+      <c r="C62" t="s">
+        <v>243</v>
+      </c>
       <c r="D62" t="s">
         <v>43</v>
       </c>
@@ -2781,6 +2868,9 @@
       <c r="B63">
         <v>22655</v>
       </c>
+      <c r="C63" t="s">
+        <v>243</v>
+      </c>
       <c r="D63" t="s">
         <v>44</v>
       </c>
@@ -2792,6 +2882,9 @@
       <c r="B64">
         <v>22623</v>
       </c>
+      <c r="C64" t="s">
+        <v>243</v>
+      </c>
       <c r="D64" t="s">
         <v>45</v>
       </c>
@@ -2803,6 +2896,9 @@
       <c r="B65">
         <v>22625</v>
       </c>
+      <c r="C65" t="s">
+        <v>243</v>
+      </c>
       <c r="D65" t="s">
         <v>46</v>
       </c>
@@ -2813,6 +2909,9 @@
       </c>
       <c r="B66">
         <v>22624</v>
+      </c>
+      <c r="C66" t="s">
+        <v>243</v>
       </c>
       <c r="D66" t="s">
         <v>47</v>
